--- a/Deals and Portfoio screen.xlsx
+++ b/Deals and Portfoio screen.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARAPL_USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7643B6-4E1C-4EAE-9C57-3131103EACBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0E0326-02D8-4FFE-A48E-E3B6111866D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="19" xr2:uid="{0386BF36-087B-4BDC-803A-227F7D8FED91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="22" xr2:uid="{0386BF36-087B-4BDC-803A-227F7D8FED91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -35,9 +35,9 @@
     <sheet name="LookUp" sheetId="21" r:id="rId20"/>
     <sheet name="Fields required or Mandatory " sheetId="22" r:id="rId21"/>
     <sheet name="Tasks 06032026" sheetId="23" r:id="rId22"/>
+    <sheet name="Testing 06052026" sheetId="26" r:id="rId23"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
     <externalReference r:id="rId26"/>
@@ -45,6 +45,7 @@
     <externalReference r:id="rId28"/>
     <externalReference r:id="rId29"/>
     <externalReference r:id="rId30"/>
+    <externalReference r:id="rId31"/>
   </externalReferences>
   <definedNames>
     <definedName name="__123Graph_ACURRENT" hidden="1">'[1]AA-2a'!#REF!</definedName>
@@ -1929,7 +1930,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9289" uniqueCount="2602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9388" uniqueCount="2647">
   <si>
     <t>Report Type</t>
   </si>
@@ -10825,6 +10826,143 @@
   </si>
   <si>
     <t>SELECT Probability, AggLoss  FROM UI_EPCurve</t>
+  </si>
+  <si>
+    <t>Screen</t>
+  </si>
+  <si>
+    <t>ILS Child Terms</t>
+  </si>
+  <si>
+    <t>Import Loss set</t>
+  </si>
+  <si>
+    <t>Associate Loss set</t>
+  </si>
+  <si>
+    <t>Run analysis</t>
+  </si>
+  <si>
+    <t>Results Screen</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pricing </t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Input Used</t>
+  </si>
+  <si>
+    <t>PortoflioReport</t>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>Matterhorn Re Ltd / Insurer / 2026</t>
+  </si>
+  <si>
+    <t>Edited the Insurer and rating</t>
+  </si>
+  <si>
+    <t>Wokring Fine</t>
+  </si>
+  <si>
+    <t>Deleted one of the Sponsor</t>
+  </si>
+  <si>
+    <t>Sponsor gor removed after asked for one more confirmation</t>
+  </si>
+  <si>
+    <t>When I clicked add, there is a small yellow pop up came and gone for 30 secs</t>
+  </si>
+  <si>
+    <t>Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Added and got refreshed</t>
+  </si>
+  <si>
+    <t>Sponsor Type shouldn’t be mandatory</t>
+  </si>
+  <si>
+    <t>Secrutiy Type</t>
+  </si>
+  <si>
+    <t>It is still not showing the drop down with security type as CAT Bond, ILW, Side car etc. How we control what goes in for class and serios. It is good to keep as example next to the label?
+There is an option to select in loss basis as "Annual Aggregate" but it is not gettign selected. also it has Annual aggreagte as well as Aggregate. what is the difference?
+Covered peril is displayed as 1 after saving the form</t>
+  </si>
+  <si>
+    <t>Cusip isthere in both ILSData and ilsterms. Do we need input from user twice?  It should be in terms alone</t>
+  </si>
+  <si>
+    <t>Deleted a ILSTerm</t>
+  </si>
+  <si>
+    <t>Working fine with a warning</t>
+  </si>
+  <si>
+    <t>When I import partial data for ilsterms, still it allows me to save the partial information wo askign me to key in madatory field.</t>
+  </si>
+  <si>
+    <t>Peril Decription</t>
+  </si>
+  <si>
+    <t>Showing number instead of peril Description</t>
+  </si>
+  <si>
+    <t>Applies to area name</t>
+  </si>
+  <si>
+    <t>Showing number instead of Region description</t>
+  </si>
+  <si>
+    <t>AppliesareaSID</t>
+  </si>
+  <si>
+    <t>This field shouldn’t be seen in UI</t>
+  </si>
+  <si>
+    <t>We should have perilset code in the Backend with data but peril information should be shown under PerilDescription</t>
+  </si>
+  <si>
+    <t>Disbled fields</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>These should be greyed out instead of blank?</t>
+  </si>
+  <si>
+    <t>Certain fileds like Basis, Trigger type, limit,Annual spread</t>
+  </si>
+  <si>
+    <t>These fields are greyout and now allowed to edit and it shouldn’t be the case</t>
+  </si>
+  <si>
+    <t>Drop down  is still not as per the lookup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It has same set of information as ILSTerms . It is not allowing to add certain fields as it is picking those from ILSterms. Form should be renamed as it saying ILSTerms and its confusing. </t>
+  </si>
+  <si>
+    <t>Peril and region should be multi selected. Don’t see any message after importing loss set</t>
+  </si>
+  <si>
+    <t>No Message after associate Loss set</t>
+  </si>
+  <si>
+    <t>Why we are having peril and region selection here. What is the purpose.</t>
+  </si>
+  <si>
+    <t>Why there are three ActivityID for one tasks</t>
   </si>
 </sst>
 </file>
@@ -12306,7 +12444,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="590">
+  <cellXfs count="591">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -13337,6 +13475,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -13634,7 +13773,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>[8]Sheet4!$D$77:$D$84</c:f>
+              <c:f>[7]Sheet4!$D$77:$D$84</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="8"/>
@@ -13673,7 +13812,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>[8]Sheet4!$D$76</c15:sqref>
+                          <c15:sqref>[7]Sheet4!$D$76</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -13694,7 +13833,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>[8]Sheet4!$C$77:$C$84</c15:sqref>
+                          <c15:sqref>[7]Sheet4!$C$77:$C$84</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -14061,7 +14200,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>[8]Sheet4!$I$77:$I$84</c:f>
+              <c:f>[7]Sheet4!$I$77:$I$84</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -14101,7 +14240,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>[8]Sheet4!$I$76</c15:sqref>
+                          <c15:sqref>[7]Sheet4!$I$76</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -14122,7 +14261,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>[8]Sheet4!$C$77:$C$84</c15:sqref>
+                          <c15:sqref>[7]Sheet4!$C$77:$C$84</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -14478,7 +14617,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>[7]Sheet1!$B$2:$B$13</c:f>
+              <c:f>[8]Sheet1!$B$2:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -14529,7 +14668,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>[7]Sheet1!$B$1</c15:sqref>
+                          <c15:sqref>[8]Sheet1!$B$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -14550,7 +14689,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>[7]Sheet1!$A$2:$A$13</c15:sqref>
+                          <c15:sqref>[8]Sheet1!$A$2:$A$13</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -23295,7 +23434,7 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet4"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -23308,7 +23447,7 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Sheet4"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -31273,7 +31412,7 @@
       <c r="L14" s="93" t="s">
         <v>264</v>
       </c>
-      <c r="M14" s="93" t="s">
+      <c r="M14" s="99" t="s">
         <v>149</v>
       </c>
       <c r="N14" s="93" t="s">
@@ -31323,7 +31462,7 @@
       <c r="L15" s="93">
         <v>0</v>
       </c>
-      <c r="M15" s="93">
+      <c r="M15" s="99">
         <v>56</v>
       </c>
       <c r="N15" s="93">
@@ -60250,11 +60389,9 @@
         <v>1</v>
       </c>
       <c r="S33" s="93" t="s">
-        <v>1457</v>
-      </c>
-      <c r="T33" s="93" t="s">
-        <v>1457</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="T33" s="93"/>
       <c r="AT33" s="93">
         <v>24</v>
       </c>
@@ -63350,6 +63487,460 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A63216-1D76-4B71-8CA5-1D38BBFCC653}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2611</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="590" t="s">
+        <v>2622</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="C4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2615</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5" t="s">
+        <v>598</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="115.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>960</v>
+      </c>
+      <c r="C6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2623</v>
+      </c>
+      <c r="E6" s="436" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" t="s">
+        <v>596</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C10" t="s">
+        <v>596</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="436" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11" t="s">
+        <v>596</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="436" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2629</v>
+      </c>
+      <c r="E12" s="436" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E13" s="436" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2633</v>
+      </c>
+      <c r="E14" s="436" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="436" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.8">
+      <c r="C16" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E16" s="436" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="C17" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2636</v>
+      </c>
+      <c r="E17" s="436" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8">
+      <c r="C18" t="s">
+        <v>275</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2639</v>
+      </c>
+      <c r="E18" s="436" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="C19" t="s">
+        <v>598</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2626</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="43.2">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2603</v>
+      </c>
+      <c r="C20" t="s">
+        <v>596</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E20" s="436" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="C21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="C22" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C24" t="s">
+        <v>596</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="C25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="C26" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="C29" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C31" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="C32" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C33" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="C34" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="C36" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="C37" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C38" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="C39" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="C40" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C41" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="C42" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="C43" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C44" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="C45" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="C46" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/Deals and Portfoio screen.xlsx
+++ b/Deals and Portfoio screen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARAPL_USER\Desktop\UI Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA170C0E-77B2-4FCE-ACC9-9767BCFBAC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34EE1069-3F0D-4134-82D1-9727483E807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="22" xr2:uid="{0386BF36-087B-4BDC-803A-227F7D8FED91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="23" xr2:uid="{0386BF36-087B-4BDC-803A-227F7D8FED91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -36,9 +36,9 @@
     <sheet name="Fields required or Mandatory " sheetId="22" r:id="rId21"/>
     <sheet name="Tasks 06032026" sheetId="23" r:id="rId22"/>
     <sheet name="06112026" sheetId="26" r:id="rId23"/>
+    <sheet name="rule" sheetId="27" r:id="rId24"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
     <externalReference r:id="rId26"/>
     <externalReference r:id="rId27"/>
@@ -46,6 +46,8 @@
     <externalReference r:id="rId29"/>
     <externalReference r:id="rId30"/>
     <externalReference r:id="rId31"/>
+    <externalReference r:id="rId32"/>
+    <externalReference r:id="rId33"/>
   </externalReferences>
   <definedNames>
     <definedName name="__123Graph_ACURRENT" hidden="1">'[1]AA-2a'!#REF!</definedName>
@@ -153,6 +155,7 @@
     <definedName name="_Fill" hidden="1">#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Fields required or Mandatory '!$AT$9:$AY$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">LookUp!$AQ$3:$AT$289</definedName>
+    <definedName name="_JNR0003" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Losses"}</definedName>
     <definedName name="_JNR0003" hidden="1">{#N/A,#N/A,FALSE,"Losses"}</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Order2" hidden="1">255</definedName>
@@ -164,6 +167,7 @@
     <definedName name="ACwvu.OPERATING._.EXPENSES." hidden="1">#REF!</definedName>
     <definedName name="agghh" hidden="1">#REF!</definedName>
     <definedName name="Aggregate_Limit__100">#REF!</definedName>
+    <definedName name="aima" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"WRKP - Cover Sheet";#N/A,#N/A,FALSE,"Liquidity Margin";#N/A,#N/A,FALSE,"Solvency Margin";#N/A,#N/A,FALSE,"Maximum Dividend";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Cashbook";#N/A,#N/A,FALSE,"Time Deposits - BOB &amp; FC";#N/A,#N/A,FALSE,"Union Bank of Switzerland";#N/A,#N/A,FALSE,"Loss Schedule"}</definedName>
     <definedName name="aima" hidden="1">{#N/A,#N/A,FALSE,"WRKP - Cover Sheet";#N/A,#N/A,FALSE,"Liquidity Margin";#N/A,#N/A,FALSE,"Solvency Margin";#N/A,#N/A,FALSE,"Maximum Dividend";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Cashbook";#N/A,#N/A,FALSE,"Time Deposits - BOB &amp; FC";#N/A,#N/A,FALSE,"Union Bank of Switzerland";#N/A,#N/A,FALSE,"Loss Schedule"}</definedName>
     <definedName name="AIR_ARe_CipherID">#REF!</definedName>
     <definedName name="AIR_ARe_LayerID">#REF!</definedName>
@@ -171,6 +175,7 @@
     <definedName name="Bond_Price__Binding">#REF!</definedName>
     <definedName name="Bound_Date">#REF!</definedName>
     <definedName name="BrokerInfo">OFFSET(#REF!, 0, 0, COUNTA(#REF!), 1)</definedName>
+    <definedName name="Buttress" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALANCE";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"ROI";#N/A,#N/A,FALSE,"EPR &amp; UEPR";#N/A,#N/A,FALSE,"DEFREIN-UEPR";#N/A,#N/A,FALSE,"ACCRUED EXPENSES";#N/A,#N/A,FALSE,"PREPAIDS";#N/A,#N/A,FALSE,"OVAL&amp;S.WK1";#N/A,#N/A,FALSE,"Maximum Dividend"}</definedName>
     <definedName name="Buttress" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALANCE";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"ROI";#N/A,#N/A,FALSE,"EPR &amp; UEPR";#N/A,#N/A,FALSE,"DEFREIN-UEPR";#N/A,#N/A,FALSE,"ACCRUED EXPENSES";#N/A,#N/A,FALSE,"PREPAIDS";#N/A,#N/A,FALSE,"OVAL&amp;S.WK1";#N/A,#N/A,FALSE,"Maximum Dividend"}</definedName>
     <definedName name="BuySell">#REF!</definedName>
     <definedName name="CalculationType">#REF!</definedName>
@@ -178,6 +183,7 @@
     <definedName name="Co_TVAR_100">'[3]Bound Portfolio Report'!$BR$8:$BR$10000</definedName>
     <definedName name="Co_TVAR_1000">'[3]Bound Portfolio Report'!$AV$8:$AV$10000</definedName>
     <definedName name="Co_TVAR_1000__seasonal">'[4]Bound Portfolio Report'!$CN$8:$CN$10000</definedName>
+    <definedName name="COdogno" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Ix";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"IS_YTD";#N/A,#N/A,FALSE,"Nt1";#N/A,#N/A,FALSE,"Nt 2";#N/A,#N/A,FALSE,"Nt 3";#N/A,#N/A,FALSE,"Nt 4";#N/A,#N/A,FALSE,"Nt 4 summary"}</definedName>
     <definedName name="COdogno" hidden="1">{#N/A,#N/A,FALSE,"Ix";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"IS_YTD";#N/A,#N/A,FALSE,"Nt1";#N/A,#N/A,FALSE,"Nt 2";#N/A,#N/A,FALSE,"Nt 3";#N/A,#N/A,FALSE,"Nt 4";#N/A,#N/A,FALSE,"Nt 4 summary"}</definedName>
     <definedName name="Collateral__Fronted">#REF!</definedName>
     <definedName name="Collateral_Fee">#REF!</definedName>
@@ -195,8 +201,10 @@
     <definedName name="Fronting_Fee">#REF!</definedName>
     <definedName name="Guideline_Check">#REF!</definedName>
     <definedName name="h" hidden="1">#REF!</definedName>
+    <definedName name="Hannover" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALANCE";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"ROI";#N/A,#N/A,FALSE,"EPR &amp; UEPR";#N/A,#N/A,FALSE,"DEFREIN-UEPR";#N/A,#N/A,FALSE,"ACCRUED EXPENSES";#N/A,#N/A,FALSE,"PREPAIDS";#N/A,#N/A,FALSE,"OVAL&amp;S.WK1";#N/A,#N/A,FALSE,"Maximum Dividend"}</definedName>
     <definedName name="Hannover" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALANCE";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"ROI";#N/A,#N/A,FALSE,"EPR &amp; UEPR";#N/A,#N/A,FALSE,"DEFREIN-UEPR";#N/A,#N/A,FALSE,"ACCRUED EXPENSES";#N/A,#N/A,FALSE,"PREPAIDS";#N/A,#N/A,FALSE,"OVAL&amp;S.WK1";#N/A,#N/A,FALSE,"Maximum Dividend"}</definedName>
     <definedName name="Hedges">#REF!</definedName>
+    <definedName name="hgh" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Procedures";#N/A,#N/A,FALSE,"A-Balance Sheet";#N/A,#N/A,FALSE,"B- Valuation Analysis";#N/A,#N/A,FALSE,"Cash";#N/A,#N/A,FALSE,"Hot Cash ";#N/A,#N/A,FALSE,"C- Income accruals";#N/A,#N/A,FALSE,"D-Expense accruals";#N/A,#N/A,FALSE,"FEES";#N/A,#N/A,FALSE,"Fund Notes"}</definedName>
     <definedName name="hgh" hidden="1">{#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Procedures";#N/A,#N/A,FALSE,"A-Balance Sheet";#N/A,#N/A,FALSE,"B- Valuation Analysis";#N/A,#N/A,FALSE,"Cash";#N/A,#N/A,FALSE,"Hot Cash ";#N/A,#N/A,FALSE,"C- Income accruals";#N/A,#N/A,FALSE,"D-Expense accruals";#N/A,#N/A,FALSE,"FEES";#N/A,#N/A,FALSE,"Fund Notes"}</definedName>
     <definedName name="ILSName">'[3]Bound Portfolio Report'!$G$8:$G$10000</definedName>
     <definedName name="Indiv_Risk_Limit">'[4]Bound Portfolio Report'!$BK$8:$BK$10000</definedName>
@@ -230,6 +238,7 @@
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
     <definedName name="Issuer">#REF!</definedName>
     <definedName name="j" hidden="1">#REF!</definedName>
+    <definedName name="jnl" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Investment Income Summary";#N/A,#N/A,FALSE,"Schroders Portfolio";#N/A,#N/A,FALSE,"Schroders Disposals";#N/A,#N/A,FALSE,"Schroders Working Paper";#N/A,#N/A,FALSE,"NatWest Portfolio";#N/A,#N/A,FALSE,"NatWest Disposals";#N/A,#N/A,FALSE,"NatWest matured FX";#N/A,#N/A,FALSE,"NatWest Working Paper"}</definedName>
     <definedName name="jnl" hidden="1">{#N/A,#N/A,FALSE,"Investment Income Summary";#N/A,#N/A,FALSE,"Schroders Portfolio";#N/A,#N/A,FALSE,"Schroders Disposals";#N/A,#N/A,FALSE,"Schroders Working Paper";#N/A,#N/A,FALSE,"NatWest Portfolio";#N/A,#N/A,FALSE,"NatWest Disposals";#N/A,#N/A,FALSE,"NatWest matured FX";#N/A,#N/A,FALSE,"NatWest Working Paper"}</definedName>
     <definedName name="k" hidden="1">#REF!</definedName>
     <definedName name="l" hidden="1">#REF!</definedName>
@@ -237,12 +246,16 @@
     <definedName name="Layer_with_participation">#REF!</definedName>
     <definedName name="Layer_with_updated_expiry">#REF!</definedName>
     <definedName name="Loss_Ratio">#REF!</definedName>
+    <definedName name="LossBasis" localSheetId="23">[9]LookUp!$A$11:$A$14</definedName>
     <definedName name="LossBasis">LookUp!$A$11:$A$14</definedName>
+    <definedName name="MacthLoss" localSheetId="23">[9]LookUp!$A$17:$A$18</definedName>
     <definedName name="MacthLoss">LookUp!$A$17:$A$18</definedName>
     <definedName name="MaxContLiab">'[4]Bound Portfolio Report'!$CQ$8:$CQ$10000</definedName>
     <definedName name="ModelingAgent">#REF!</definedName>
     <definedName name="Name">#REF!</definedName>
+    <definedName name="Nav" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="Nav" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
+    <definedName name="no" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Investment Income Summary";#N/A,#N/A,FALSE,"Schroders Portfolio";#N/A,#N/A,FALSE,"Schroders Disposals";#N/A,#N/A,FALSE,"Schroders Working Paper";#N/A,#N/A,FALSE,"NatWest Portfolio";#N/A,#N/A,FALSE,"NatWest Disposals";#N/A,#N/A,FALSE,"NatWest matured FX";#N/A,#N/A,FALSE,"NatWest Working Paper"}</definedName>
     <definedName name="no" hidden="1">{#N/A,#N/A,FALSE,"Investment Income Summary";#N/A,#N/A,FALSE,"Schroders Portfolio";#N/A,#N/A,FALSE,"Schroders Disposals";#N/A,#N/A,FALSE,"Schroders Working Paper";#N/A,#N/A,FALSE,"NatWest Portfolio";#N/A,#N/A,FALSE,"NatWest Disposals";#N/A,#N/A,FALSE,"NatWest matured FX";#N/A,#N/A,FALSE,"NatWest Working Paper"}</definedName>
     <definedName name="Non_Modeled___PIMCO_View">#REF!</definedName>
     <definedName name="Notional">'[4]Bound Portfolio Report'!$H$3</definedName>
@@ -257,12 +270,15 @@
     <definedName name="PIMCO_Occ_Limit">'[3]Bound Portfolio Report'!$AB$8:$AB$10000</definedName>
     <definedName name="PIMCO_Share">'[3]Bound Portfolio Report'!$AP$8:$AP$10000</definedName>
     <definedName name="PortfolioName">#REF!</definedName>
+    <definedName name="ppdoo" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"COVER.XLS";#N/A,#N/A,FALSE,"STDBS.XLS";#N/A,#N/A,FALSE,"STDPL.XLS";#N/A,#N/A,FALSE,"NOTES.XLS"}</definedName>
     <definedName name="ppdoo" hidden="1">{#N/A,#N/A,FALSE,"COVER.XLS";#N/A,#N/A,FALSE,"STDBS.XLS";#N/A,#N/A,FALSE,"STDPL.XLS";#N/A,#N/A,FALSE,"NOTES.XLS"}</definedName>
     <definedName name="Premium">'[3]Bound Portfolio Report'!$AU$8:$AU$10000</definedName>
     <definedName name="Profit">#REF!</definedName>
+    <definedName name="ProgramType" localSheetId="23">[9]LookUp!$A$21:$A$26</definedName>
     <definedName name="ProgramType">LookUp!$A$21:$A$26</definedName>
     <definedName name="qt43tgreh4yu46w46w" hidden="1">#REF!</definedName>
     <definedName name="Quantity_Pledged">'[4]Bound Portfolio Report'!XFD1:XFD9996</definedName>
+    <definedName name="ReinsuranceTypeCode" localSheetId="23">[9]LookUp!$A$3:$A$6</definedName>
     <definedName name="ReinsuranceTypeCode">LookUp!$A$3:$A$7</definedName>
     <definedName name="ReportTables_NumberingType" hidden="1">2</definedName>
     <definedName name="Return">#REF!</definedName>
@@ -314,46 +330,84 @@
     <definedName name="Swvu.grid._.lines." hidden="1">[5]JE!#REF!</definedName>
     <definedName name="Swvu.OPERATING._.EXPENSES." hidden="1">#REF!</definedName>
     <definedName name="t" hidden="1">#REF!</definedName>
+    <definedName name="Triggertype" localSheetId="23">[9]LookUp!$C$11:$C$13</definedName>
     <definedName name="Triggertype">LookUp!$C$11:$C$13</definedName>
     <definedName name="TTM">#REF!</definedName>
+    <definedName name="UPSRE" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Ix";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"IS_YTD";#N/A,#N/A,FALSE,"Nt1";#N/A,#N/A,FALSE,"Nt 2";#N/A,#N/A,FALSE,"Nt 3";#N/A,#N/A,FALSE,"Nt 4";#N/A,#N/A,FALSE,"Nt 4 summary"}</definedName>
     <definedName name="UPSRE" hidden="1">{#N/A,#N/A,FALSE,"Ix";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"IS_YTD";#N/A,#N/A,FALSE,"Nt1";#N/A,#N/A,FALSE,"Nt 2";#N/A,#N/A,FALSE,"Nt 3";#N/A,#N/A,FALSE,"Nt 4";#N/A,#N/A,FALSE,"Nt 4 summary"}</definedName>
     <definedName name="UW_Expenses">#REF!</definedName>
+    <definedName name="UWSummary1996" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="UWSummary1996" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
+    <definedName name="UWSUMMARY1997" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="UWSUMMARY1997" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
+    <definedName name="UWSummary1998" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="UWSummary1998" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
+    <definedName name="UWSUMMARY1999" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="UWSUMMARY1999" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="w" hidden="1">#REF!</definedName>
+    <definedName name="warren" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"1Qtr98";#N/A,#N/A,FALSE,"Mellon Trust Payment";#N/A,#N/A,FALSE,"Time Deposits US$"}</definedName>
     <definedName name="warren" hidden="1">{#N/A,#N/A,FALSE,"1Qtr98";#N/A,#N/A,FALSE,"Mellon Trust Payment";#N/A,#N/A,FALSE,"Time Deposits US$"}</definedName>
+    <definedName name="wnr.notes" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"ASLCASH"}</definedName>
     <definedName name="wnr.notes" hidden="1">{#N/A,#N/A,FALSE,"ASLCASH"}</definedName>
+    <definedName name="wrn.cash." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"1Qtr98";#N/A,#N/A,FALSE,"Mellon Trust Payment";#N/A,#N/A,FALSE,"Time Deposits US$"}</definedName>
     <definedName name="wrn.cash." hidden="1">{#N/A,#N/A,FALSE,"1Qtr98";#N/A,#N/A,FALSE,"Mellon Trust Payment";#N/A,#N/A,FALSE,"Time Deposits US$"}</definedName>
+    <definedName name="wrn.Cash._.book." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Current &amp; Demand";#N/A,#N/A,FALSE,"Buttress fund 98 "}</definedName>
     <definedName name="wrn.Cash._.book." hidden="1">{#N/A,#N/A,FALSE,"Current &amp; Demand";#N/A,#N/A,FALSE,"Buttress fund 98 "}</definedName>
+    <definedName name="wrn.CODOGNO._.Print._.all." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS"}</definedName>
     <definedName name="wrn.CODOGNO._.Print._.all." hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS"}</definedName>
+    <definedName name="wrn.Draft._.stmts." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover Sheet";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investments";#N/A,#N/A,FALSE,"Underwriting Summary";#N/A,#N/A,FALSE,"Underwriting - Corporate";#N/A,#N/A,FALSE,"Underwriting - Dealer";#N/A,#N/A,FALSE,"Aggregate Stoploss";#N/A,#N/A,FALSE,"Corp - losses";#N/A,#N/A,FALSE,"Dealer - losses"}</definedName>
     <definedName name="wrn.Draft._.stmts." hidden="1">{#N/A,#N/A,FALSE,"Cover Sheet";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investments";#N/A,#N/A,FALSE,"Underwriting Summary";#N/A,#N/A,FALSE,"Underwriting - Corporate";#N/A,#N/A,FALSE,"Underwriting - Dealer";#N/A,#N/A,FALSE,"Aggregate Stoploss";#N/A,#N/A,FALSE,"Corp - losses";#N/A,#N/A,FALSE,"Dealer - losses"}</definedName>
+    <definedName name="wrn.Financial._.Statements." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"TB";#N/A,#N/A,FALSE,"COVER ";#N/A,#N/A,FALSE,"CONTENTS";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"IS-QRTLY";#N/A,#N/A,FALSE,"CF";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"YTD";#N/A,#N/A,FALSE,"ITD";#N/A,#N/A,FALSE,"2001-98";#N/A,#N/A,FALSE,"1001-99";#N/A,#N/A,FALSE,"1001-02";#N/A,#N/A,FALSE,"1002-1004-99";#N/A,#N/A,FALSE,"1002-1004-02";#N/A,#N/A,FALSE,"1005-99";#N/A,#N/A,FALSE,"1005-02";#N/A,#N/A,FALSE,"1006-99";#N/A,#N/A,FALSE,"1006-02";#N/A,#N/A,FALSE,"2002-99";#N/A,#N/A,FALSE,"2002-02";#N/A,#N/A,FALSE,"2003-99";#N/A,#N/A,FALSE,"2003-02";#N/A,#N/A,FALSE,"2004-99TRIP";#N/A,#N/A,FALSE,"2004-99Interruption";#N/A,#N/A,FALSE,"2004-99Cancellation";#N/A,#N/A,FALSE,"StopLoss";#N/A,#N/A,FALSE,"ACIA-Castle";#N/A,#N/A,FALSE,"RATIOS"}</definedName>
     <definedName name="wrn.Financial._.Statements." hidden="1">{#N/A,#N/A,FALSE,"TB";#N/A,#N/A,FALSE,"COVER ";#N/A,#N/A,FALSE,"CONTENTS";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"IS-QRTLY";#N/A,#N/A,FALSE,"CF";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"YTD";#N/A,#N/A,FALSE,"ITD";#N/A,#N/A,FALSE,"2001-98";#N/A,#N/A,FALSE,"1001-99";#N/A,#N/A,FALSE,"1001-02";#N/A,#N/A,FALSE,"1002-1004-99";#N/A,#N/A,FALSE,"1002-1004-02";#N/A,#N/A,FALSE,"1005-99";#N/A,#N/A,FALSE,"1005-02";#N/A,#N/A,FALSE,"1006-99";#N/A,#N/A,FALSE,"1006-02";#N/A,#N/A,FALSE,"2002-99";#N/A,#N/A,FALSE,"2002-02";#N/A,#N/A,FALSE,"2003-99";#N/A,#N/A,FALSE,"2003-02";#N/A,#N/A,FALSE,"2004-99TRIP";#N/A,#N/A,FALSE,"2004-99Interruption";#N/A,#N/A,FALSE,"2004-99Cancellation";#N/A,#N/A,FALSE,"StopLoss";#N/A,#N/A,FALSE,"ACIA-Castle";#N/A,#N/A,FALSE,"RATIOS"}</definedName>
+    <definedName name="wrn.Financial._.Stetements." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Contents";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"p&amp;l";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"underwriting analysis";#N/A,#N/A,FALSE,"Solvency"}</definedName>
     <definedName name="wrn.Financial._.Stetements." hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Contents";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"p&amp;l";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"underwriting analysis";#N/A,#N/A,FALSE,"Solvency"}</definedName>
+    <definedName name="wrn.FINANCIALS." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
     <definedName name="wrn.FINANCIALS." hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"income";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"deposits";#N/A,#N/A,FALSE,"uwytd";#N/A,#N/A,FALSE,"g &amp; a";#N/A,#N/A,FALSE,"uwincept"}</definedName>
+    <definedName name="wrn.FreeportIfs." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"Commentary";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"p&amp;l";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"Solvency"}</definedName>
     <definedName name="wrn.FreeportIfs." hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"Commentary";#N/A,#N/A,FALSE,"balance";#N/A,#N/A,FALSE,"p&amp;l";#N/A,#N/A,FALSE,"notes";#N/A,#N/A,FALSE,"Solvency"}</definedName>
+    <definedName name="wrn.FS." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Contents";#N/A,#N/A,FALSE,"BS-Con";#N/A,#N/A,FALSE,"BS-Detail";#N/A,#N/A,FALSE,"IS-Con";#N/A,#N/A,FALSE,"IS-Detail";#N/A,#N/A,FALSE,"IS-Via";#N/A,#N/A,FALSE,"IS-Bliss";#N/A,#N/A,FALSE,"IS-Tort";#N/A,#N/A,FALSE,"IS-FP";#N/A,#N/A,FALSE,"IS-Wob";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"S1";#N/A,#N/A,FALSE,"S2";#N/A,#N/A,FALSE,"S3"}</definedName>
     <definedName name="wrn.FS." hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Contents";#N/A,#N/A,FALSE,"BS-Con";#N/A,#N/A,FALSE,"BS-Detail";#N/A,#N/A,FALSE,"IS-Con";#N/A,#N/A,FALSE,"IS-Detail";#N/A,#N/A,FALSE,"IS-Via";#N/A,#N/A,FALSE,"IS-Bliss";#N/A,#N/A,FALSE,"IS-Tort";#N/A,#N/A,FALSE,"IS-FP";#N/A,#N/A,FALSE,"IS-Wob";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"S1";#N/A,#N/A,FALSE,"S2";#N/A,#N/A,FALSE,"S3"}</definedName>
+    <definedName name="wrn.Granite._.Mgmt._.Financials." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Fly";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"PL";#N/A,#N/A,FALSE,"Note1";#N/A,#N/A,FALSE,"Sch1";#N/A,#N/A,FALSE,"Sch2";#N/A,#N/A,FALSE,"Sch3";#N/A,#N/A,FALSE,"Sch4"}</definedName>
     <definedName name="wrn.Granite._.Mgmt._.Financials." hidden="1">{#N/A,#N/A,FALSE,"Fly";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"PL";#N/A,#N/A,FALSE,"Note1";#N/A,#N/A,FALSE,"Sch1";#N/A,#N/A,FALSE,"Sch2";#N/A,#N/A,FALSE,"Sch3";#N/A,#N/A,FALSE,"Sch4"}</definedName>
+    <definedName name="wrn.Haul._.Month._.End." localSheetId="23" hidden="1">{#N/A,#N/A,TRUE,"BS";#N/A,#N/A,TRUE,"IS";#N/A,#N/A,TRUE,"NOTES";#N/A,#N/A,TRUE,"UW"}</definedName>
     <definedName name="wrn.Haul._.Month._.End." hidden="1">{#N/A,#N/A,TRUE,"BS";#N/A,#N/A,TRUE,"IS";#N/A,#N/A,TRUE,"NOTES";#N/A,#N/A,TRUE,"UW"}</definedName>
+    <definedName name="wrn.INVESTMENTS." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"FAIBF";#N/A,#N/A,FALSE,"BARINGS";#N/A,#N/A,FALSE,"PARIBAS";#N/A,#N/A,FALSE,"VOYAGER";#N/A,#N/A,FALSE,"CIF";#N/A,#N/A,FALSE,"ALL"}</definedName>
     <definedName name="wrn.INVESTMENTS." hidden="1">{#N/A,#N/A,FALSE,"FAIBF";#N/A,#N/A,FALSE,"BARINGS";#N/A,#N/A,FALSE,"PARIBAS";#N/A,#N/A,FALSE,"VOYAGER";#N/A,#N/A,FALSE,"CIF";#N/A,#N/A,FALSE,"ALL"}</definedName>
+    <definedName name="wrn.Liquidity._.and._.Solvency._.Margins." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Liq";#N/A,#N/A,FALSE,"Solv";#N/A,#N/A,FALSE,"MaxDiv"}</definedName>
     <definedName name="wrn.Liquidity._.and._.Solvency._.Margins." hidden="1">{#N/A,#N/A,FALSE,"Liq";#N/A,#N/A,FALSE,"Solv";#N/A,#N/A,FALSE,"MaxDiv"}</definedName>
+    <definedName name="wrn.management." localSheetId="23" hidden="1">{#N/A,#N/A,TRUE,"Cover";#N/A,#N/A,TRUE,"Bal.Sht";#N/A,#N/A,TRUE,"Inc.Stmt";#N/A,#N/A,TRUE,"Inc.Stmt - Qtr";#N/A,#N/A,TRUE,"FS.Notes";#N/A,#N/A,TRUE,"Short term inv";#N/A,#N/A,TRUE,"UW analysis";#N/A,#N/A,TRUE,"G&amp;A.Sch"}</definedName>
     <definedName name="wrn.management." hidden="1">{#N/A,#N/A,TRUE,"Cover";#N/A,#N/A,TRUE,"Bal.Sht";#N/A,#N/A,TRUE,"Inc.Stmt";#N/A,#N/A,TRUE,"Inc.Stmt - Qtr";#N/A,#N/A,TRUE,"FS.Notes";#N/A,#N/A,TRUE,"Short term inv";#N/A,#N/A,TRUE,"UW analysis";#N/A,#N/A,TRUE,"G&amp;A.Sch"}</definedName>
+    <definedName name="wrn.Margins." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Liquidity Margin";#N/A,#N/A,FALSE,"Solvency Margin";#N/A,#N/A,FALSE,"Maximum Dividend"}</definedName>
     <definedName name="wrn.Margins." hidden="1">{#N/A,#N/A,FALSE,"Liquidity Margin";#N/A,#N/A,FALSE,"Solvency Margin";#N/A,#N/A,FALSE,"Maximum Dividend"}</definedName>
+    <definedName name="wrn.Mgmt._.finacial._.stmts." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover Sheet";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Loss Schedule"}</definedName>
     <definedName name="wrn.Mgmt._.finacial._.stmts." hidden="1">{#N/A,#N/A,FALSE,"Cover Sheet";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Loss Schedule"}</definedName>
+    <definedName name="wrn.mgmt._.financial._.stmts." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover Sheet";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Loss Schedule";#N/A,#N/A,FALSE,"Underwriting Analysis";#N/A,#N/A,FALSE,"AR&amp;AP Analysis"}</definedName>
     <definedName name="wrn.mgmt._.financial._.stmts." hidden="1">{#N/A,#N/A,FALSE,"Cover Sheet";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Loss Schedule";#N/A,#N/A,FALSE,"Underwriting Analysis";#N/A,#N/A,FALSE,"AR&amp;AP Analysis"}</definedName>
+    <definedName name="wrn.Penn._.FS." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"TDs(Sch.1)";#N/A,#N/A,FALSE,"UW(Sch.2)";#N/A,#N/A,FALSE,"Losses(Sch.3)";#N/A,#N/A,FALSE,"G&amp;A(Sch.4)";#N/A,#N/A,FALSE,"Stat"}</definedName>
     <definedName name="wrn.Penn._.FS." hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"TDs(Sch.1)";#N/A,#N/A,FALSE,"UW(Sch.2)";#N/A,#N/A,FALSE,"Losses(Sch.3)";#N/A,#N/A,FALSE,"G&amp;A(Sch.4)";#N/A,#N/A,FALSE,"Stat"}</definedName>
+    <definedName name="wrn.ppwps9903.xls." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Losses"}</definedName>
     <definedName name="wrn.ppwps9903.xls." hidden="1">{#N/A,#N/A,FALSE,"Losses"}</definedName>
+    <definedName name="wrn.Print._.Stat._.Return." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Introduction";#N/A,#N/A,FALSE,"Declaration of Stat ratios";#N/A,#N/A,FALSE,"Solvency Certificate";#N/A,#N/A,FALSE,"Form 1";#N/A,#N/A,FALSE,"Form 2";#N/A,#N/A,FALSE,"Form 8";#N/A,#N/A,FALSE,"Ratios"}</definedName>
     <definedName name="wrn.Print._.Stat._.Return." hidden="1">{#N/A,#N/A,FALSE,"Introduction";#N/A,#N/A,FALSE,"Declaration of Stat ratios";#N/A,#N/A,FALSE,"Solvency Certificate";#N/A,#N/A,FALSE,"Form 1";#N/A,#N/A,FALSE,"Form 2";#N/A,#N/A,FALSE,"Form 8";#N/A,#N/A,FALSE,"Ratios"}</definedName>
+    <definedName name="wrn.report." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"J&amp;H policy #'s";#N/A,#N/A,FALSE,"ROI";#N/A,#N/A,FALSE,"UW Analysis @ 6.30.96";#N/A,#N/A,FALSE,"UW Analysis @ 3.31.96";#N/A,#N/A,FALSE,"9596 Loss Summary";#N/A,#N/A,FALSE,"9596 &amp; 9697 Prop Loss";#N/A,#N/A,FALSE,"9596 &amp; 9697 Marine Loss";#N/A,#N/A,FALSE,"3.31.96 Prop Loss per J&amp;H";#N/A,#N/A,FALSE,"3.31.96 Mar Loss per J&amp;H"}</definedName>
     <definedName name="wrn.report." hidden="1">{#N/A,#N/A,FALSE,"J&amp;H policy #'s";#N/A,#N/A,FALSE,"ROI";#N/A,#N/A,FALSE,"UW Analysis @ 6.30.96";#N/A,#N/A,FALSE,"UW Analysis @ 3.31.96";#N/A,#N/A,FALSE,"9596 Loss Summary";#N/A,#N/A,FALSE,"9596 &amp; 9697 Prop Loss";#N/A,#N/A,FALSE,"9596 &amp; 9697 Marine Loss";#N/A,#N/A,FALSE,"3.31.96 Prop Loss per J&amp;H";#N/A,#N/A,FALSE,"3.31.96 Mar Loss per J&amp;H"}</definedName>
+    <definedName name="wrn.Stainless._.FS." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"Contents";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"Underwriting Analysis";#N/A,#N/A,FALSE,"Solvency"}</definedName>
     <definedName name="wrn.Stainless._.FS." hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"Contents";#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"P&amp;L";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"Underwriting Analysis";#N/A,#N/A,FALSE,"Solvency"}</definedName>
+    <definedName name="wrn.Standard._.NAV._.Package." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Procedures";#N/A,#N/A,FALSE,"A-Balance Sheet";#N/A,#N/A,FALSE,"B- Valuation Analysis";#N/A,#N/A,FALSE,"Cash";#N/A,#N/A,FALSE,"Hot Cash ";#N/A,#N/A,FALSE,"C- Income accruals";#N/A,#N/A,FALSE,"D-Expense accruals";#N/A,#N/A,FALSE,"FEES";#N/A,#N/A,FALSE,"Fund Notes"}</definedName>
     <definedName name="wrn.Standard._.NAV._.Package." hidden="1">{#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Procedures";#N/A,#N/A,FALSE,"A-Balance Sheet";#N/A,#N/A,FALSE,"B- Valuation Analysis";#N/A,#N/A,FALSE,"Cash";#N/A,#N/A,FALSE,"Hot Cash ";#N/A,#N/A,FALSE,"C- Income accruals";#N/A,#N/A,FALSE,"D-Expense accruals";#N/A,#N/A,FALSE,"FEES";#N/A,#N/A,FALSE,"Fund Notes"}</definedName>
+    <definedName name="wrn.STATEMENTS." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"STAT";#N/A,#N/A,FALSE,"BUD_qtr";#N/A,#N/A,FALSE,"BUD_ytd"}</definedName>
     <definedName name="wrn.STATEMENTS." hidden="1">{#N/A,#N/A,FALSE,"BS";#N/A,#N/A,FALSE,"IS";#N/A,#N/A,FALSE,"STAT";#N/A,#N/A,FALSE,"BUD_qtr";#N/A,#N/A,FALSE,"BUD_ytd"}</definedName>
+    <definedName name="wrn.suf._.fs." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"bs";#N/A,#N/A,FALSE,"p&amp;l";#N/A,#N/A,FALSE,"fsnotes";#N/A,#N/A,FALSE,"sched1";#N/A,#N/A,FALSE,"sched2";#N/A,#N/A,FALSE,"sched3";#N/A,#N/A,FALSE,"sched4";#N/A,#N/A,FALSE,"sched5";#N/A,#N/A,FALSE,"sched6";#N/A,#N/A,FALSE,"g&amp;a"}</definedName>
     <definedName name="wrn.suf._.fs." hidden="1">{#N/A,#N/A,FALSE,"cover";#N/A,#N/A,FALSE,"bs";#N/A,#N/A,FALSE,"p&amp;l";#N/A,#N/A,FALSE,"fsnotes";#N/A,#N/A,FALSE,"sched1";#N/A,#N/A,FALSE,"sched2";#N/A,#N/A,FALSE,"sched3";#N/A,#N/A,FALSE,"sched4";#N/A,#N/A,FALSE,"sched5";#N/A,#N/A,FALSE,"sched6";#N/A,#N/A,FALSE,"g&amp;a"}</definedName>
+    <definedName name="wrn.Underwriting._.Schedules." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"YTD";#N/A,#N/A,FALSE,"ITD";#N/A,#N/A,FALSE,"2001-98";#N/A,#N/A,FALSE,"1001-99";#N/A,#N/A,FALSE,"1001-02";#N/A,#N/A,FALSE,"1002-1004-99";#N/A,#N/A,FALSE,"1002-1004-02";#N/A,#N/A,FALSE,"1005-99";#N/A,#N/A,FALSE,"1005-02";#N/A,#N/A,FALSE,"1006-99";#N/A,#N/A,FALSE,"1006-02";#N/A,#N/A,FALSE,"2002-99";#N/A,#N/A,FALSE,"2002-02";#N/A,#N/A,FALSE,"2003-99";#N/A,#N/A,FALSE,"2003-02";#N/A,#N/A,FALSE,"2004-99TRIP";#N/A,#N/A,FALSE,"2004-99Interruption";#N/A,#N/A,FALSE,"2004-99Cancellation";#N/A,#N/A,FALSE,"StopLoss";#N/A,#N/A,FALSE,"ACIA-Castle"}</definedName>
     <definedName name="wrn.Underwriting._.Schedules." hidden="1">{#N/A,#N/A,FALSE,"YTD";#N/A,#N/A,FALSE,"ITD";#N/A,#N/A,FALSE,"2001-98";#N/A,#N/A,FALSE,"1001-99";#N/A,#N/A,FALSE,"1001-02";#N/A,#N/A,FALSE,"1002-1004-99";#N/A,#N/A,FALSE,"1002-1004-02";#N/A,#N/A,FALSE,"1005-99";#N/A,#N/A,FALSE,"1005-02";#N/A,#N/A,FALSE,"1006-99";#N/A,#N/A,FALSE,"1006-02";#N/A,#N/A,FALSE,"2002-99";#N/A,#N/A,FALSE,"2002-02";#N/A,#N/A,FALSE,"2003-99";#N/A,#N/A,FALSE,"2003-02";#N/A,#N/A,FALSE,"2004-99TRIP";#N/A,#N/A,FALSE,"2004-99Interruption";#N/A,#N/A,FALSE,"2004-99Cancellation";#N/A,#N/A,FALSE,"StopLoss";#N/A,#N/A,FALSE,"ACIA-Castle"}</definedName>
+    <definedName name="wrn.Wasatch._.mgmt._.financials." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALSHT";#N/A,#N/A,FALSE,"INCSTMT";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"SCH1INV";#N/A,#N/A,FALSE,"SCH2CONS";#N/A,#N/A,FALSE,"SCH2PROP";#N/A,#N/A,FALSE,"SCH2WC";#N/A,#N/A,FALSE,"SCH2EL";#N/A,#N/A,FALSE,"SCH3RES";#N/A,#N/A,FALSE,"SCH4G&amp;A"}</definedName>
     <definedName name="wrn.Wasatch._.mgmt._.financials." hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALSHT";#N/A,#N/A,FALSE,"INCSTMT";#N/A,#N/A,FALSE,"NOTES";#N/A,#N/A,FALSE,"SCH1INV";#N/A,#N/A,FALSE,"SCH2CONS";#N/A,#N/A,FALSE,"SCH2PROP";#N/A,#N/A,FALSE,"SCH2WC";#N/A,#N/A,FALSE,"SCH2EL";#N/A,#N/A,FALSE,"SCH3RES";#N/A,#N/A,FALSE,"SCH4G&amp;A"}</definedName>
+    <definedName name="wrn.workbook." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALSHT";#N/A,#N/A,FALSE,"INCSTMT"}</definedName>
     <definedName name="wrn.workbook." hidden="1">{#N/A,#N/A,FALSE,"COVER";#N/A,#N/A,FALSE,"BALSHT";#N/A,#N/A,FALSE,"INCSTMT"}</definedName>
+    <definedName name="wrn.Working._.paper._.financial._.stmts." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"WRKP - Cover Sheet";#N/A,#N/A,FALSE,"Liquidity Margin";#N/A,#N/A,FALSE,"Solvency Margin";#N/A,#N/A,FALSE,"Maximum Dividend";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Cashbook";#N/A,#N/A,FALSE,"Time Deposits - BOB &amp; FC";#N/A,#N/A,FALSE,"Union Bank of Switzerland";#N/A,#N/A,FALSE,"Loss Schedule"}</definedName>
     <definedName name="wrn.Working._.paper._.financial._.stmts." hidden="1">{#N/A,#N/A,FALSE,"WRKP - Cover Sheet";#N/A,#N/A,FALSE,"Liquidity Margin";#N/A,#N/A,FALSE,"Solvency Margin";#N/A,#N/A,FALSE,"Maximum Dividend";#N/A,#N/A,FALSE,"Balance Sheet";#N/A,#N/A,FALSE,"Income Statement";#N/A,#N/A,FALSE,"Notes";#N/A,#N/A,FALSE,"Investment Schedule";#N/A,#N/A,FALSE,"Cashbook";#N/A,#N/A,FALSE,"Time Deposits - BOB &amp; FC";#N/A,#N/A,FALSE,"Union Bank of Switzerland";#N/A,#N/A,FALSE,"Loss Schedule"}</definedName>
+    <definedName name="wrn.Working._.papers." localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"DATA";#N/A,#N/A,FALSE,"Solvency";#N/A,#N/A,FALSE,"Return on Investment"}</definedName>
     <definedName name="wrn.Working._.papers." hidden="1">{#N/A,#N/A,FALSE,"DATA";#N/A,#N/A,FALSE,"Solvency";#N/A,#N/A,FALSE,"Return on Investment"}</definedName>
     <definedName name="wTablePasteAs_23" hidden="1">1</definedName>
     <definedName name="wTablePasteAs_28" hidden="1">1</definedName>
@@ -424,13 +478,21 @@
     <definedName name="wTableType_7" hidden="1">2</definedName>
     <definedName name="wTableType_8" hidden="1">2</definedName>
     <definedName name="wTableType_9" hidden="1">2</definedName>
+    <definedName name="wvu.ANALYSIS._.1." localSheetId="23" hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,60,#N/A,7.86324786324786,19.6153846153846,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.ANALYSIS._.1.","ACwvu.ANALYSIS._.1.",#N/A,FALSE,FALSE,0.5,0.3,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R2C1:R61C6",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.ANALYSIS._.1." hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,60,#N/A,7.86324786324786,19.6153846153846,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.ANALYSIS._.1.","ACwvu.ANALYSIS._.1.",#N/A,FALSE,FALSE,0.5,0.3,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R2C1:R61C6",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="wvu.ANALYSIS._.2." localSheetId="23" hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,124,#N/A,7.86324786324786,19.6153846153846,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.ANALYSIS._.2.","ACwvu.ANALYSIS._.2.",#N/A,FALSE,FALSE,0.5,0.3,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R69C1:R127C6",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.ANALYSIS._.2." hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,124,#N/A,7.86324786324786,19.6153846153846,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.ANALYSIS._.2.","ACwvu.ANALYSIS._.2.",#N/A,FALSE,FALSE,0.5,0.3,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R69C1:R127C6",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="wvu.BALANCE._.SHEET." localSheetId="23" hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,129,#N/A,8.58620689655172,20.16,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.BALANCE._.SHEET.","ACwvu.BALANCE._.SHEET.",#N/A,FALSE,FALSE,0.75,0.5,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R2C1:R45C8",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.BALANCE._.SHEET." hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,129,#N/A,8.58620689655172,20.16,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.BALANCE._.SHEET.","ACwvu.BALANCE._.SHEET.",#N/A,FALSE,FALSE,0.75,0.5,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R2C1:R45C8",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="wvu.grid._.lines." localSheetId="23" hidden="1">{TRUE,TRUE,-1.25,-15.5,772.5,492.75,FALSE,TRUE,TRUE,TRUE,0,1,#N/A,1,#N/A,9.25,34.8235294117647,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.grid._.lines.","ACwvu.grid._.lines.",#N/A,FALSE,FALSE,0.75,0.75,1,1,1,"&amp;A","Page &amp;P",FALSE,FALSE,FALSE,TRUE,1,100,#N/A,#N/A,FALSE,FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,#N/A,#N/A,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.grid._.lines." hidden="1">{TRUE,TRUE,-1.25,-15.5,772.5,492.75,FALSE,TRUE,TRUE,TRUE,0,1,#N/A,1,#N/A,9.25,34.8235294117647,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.grid._.lines.","ACwvu.grid._.lines.",#N/A,FALSE,FALSE,0.75,0.75,1,1,1,"&amp;A","Page &amp;P",FALSE,FALSE,FALSE,TRUE,1,100,#N/A,#N/A,FALSE,FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,#N/A,#N/A,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="wvu.INCONE._.STATEMENT." localSheetId="23" hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,4,#N/A,114,#N/A,10.0234375,19.8846153846154,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.INCONE._.STATEMENT.","ACwvu.INCONE._.STATEMENT.",#N/A,FALSE,FALSE,0.75,0.5,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R63C1:R117C10",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.INCONE._.STATEMENT." hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,4,#N/A,114,#N/A,10.0234375,19.8846153846154,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.INCONE._.STATEMENT.","ACwvu.INCONE._.STATEMENT.",#N/A,FALSE,FALSE,0.75,0.5,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R63C1:R117C10",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="wvu.OPERATING._.EXPENSES." localSheetId="23" hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,5,#N/A,182,#N/A,10.7109375,20.96,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.OPERATING._.EXPENSES.","ACwvu.OPERATING._.EXPENSES.",#N/A,FALSE,FALSE,0.5,0.3,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R138C1:R186C10",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.OPERATING._.EXPENSES." hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,5,#N/A,182,#N/A,10.7109375,20.96,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.OPERATING._.EXPENSES.","ACwvu.OPERATING._.EXPENSES.",#N/A,FALSE,FALSE,0.5,0.3,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R138C1:R186C10",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="wvu.STATUTORY._.RATIOS." localSheetId="23" hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,184,#N/A,8.58620689655172,20.96,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.STATUTORY._.RATIOS.","ACwvu.STATUTORY._.RATIOS.",#N/A,FALSE,FALSE,0.75,0.5,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R129C1:R186C8",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
     <definedName name="wvu.STATUTORY._.RATIOS." hidden="1">{TRUE,TRUE,-0.8,-17,618,363.6,FALSE,FALSE,TRUE,TRUE,0,1,#N/A,184,#N/A,8.58620689655172,20.96,1,FALSE,FALSE,3,TRUE,1,FALSE,100,"Swvu.STATUTORY._.RATIOS.","ACwvu.STATUTORY._.RATIOS.",#N/A,FALSE,FALSE,0.75,0.5,0.5,0.55,1,"","",TRUE,TRUE,FALSE,FALSE,1,#N/A,1,1,"=R129C1:R186C8",FALSE,#N/A,#N/A,FALSE,FALSE,FALSE,1,0,0,FALSE,FALSE,TRUE,TRUE,TRUE}</definedName>
+    <definedName name="xxx" localSheetId="23" hidden="1">{#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Procedures";#N/A,#N/A,FALSE,"A-Balance Sheet";#N/A,#N/A,FALSE,"B- Valuation Analysis";#N/A,#N/A,FALSE,"Cash";#N/A,#N/A,FALSE,"Hot Cash ";#N/A,#N/A,FALSE,"C- Income accruals";#N/A,#N/A,FALSE,"D-Expense accruals";#N/A,#N/A,FALSE,"FEES";#N/A,#N/A,FALSE,"Fund Notes"}</definedName>
     <definedName name="xxx" hidden="1">{#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Procedures";#N/A,#N/A,FALSE,"A-Balance Sheet";#N/A,#N/A,FALSE,"B- Valuation Analysis";#N/A,#N/A,FALSE,"Cash";#N/A,#N/A,FALSE,"Hot Cash ";#N/A,#N/A,FALSE,"C- Income accruals";#N/A,#N/A,FALSE,"D-Expense accruals";#N/A,#N/A,FALSE,"FEES";#N/A,#N/A,FALSE,"Fund Notes"}</definedName>
     <definedName name="Z_02C5980E_9CED_11D3_8584_00A0C9DF1035_.wvu.PrintArea" hidden="1">#REF!</definedName>
     <definedName name="Z_02C5980F_9CED_11D3_8584_00A0C9DF1035_.wvu.PrintArea" hidden="1">#REF!</definedName>
@@ -1930,7 +1992,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9353" uniqueCount="2632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9924" uniqueCount="2765">
   <si>
     <t>Report Type</t>
   </si>
@@ -10917,6 +10979,405 @@
   <si>
     <t>Event ID has no model to map it back to region or peril and need to sort that one.</t>
   </si>
+  <si>
+    <t>Comparison Matrix (Enable / Fixed / Disabled)</t>
+  </si>
+  <si>
+    <t>Field in ILS Terms form</t>
+  </si>
+  <si>
+    <t>Core Structure Fields</t>
+  </si>
+  <si>
+    <t>get_terms()</t>
+  </si>
+  <si>
+    <t>Need to check the ParentRelationType criteria as it uses 4 as a condition to mark the layer as RPP</t>
+  </si>
+  <si>
+    <t>Get YELT</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Ground-Up</t>
+  </si>
+  <si>
+    <t>FHCF</t>
+  </si>
+  <si>
+    <t>Layer#</t>
+  </si>
+  <si>
+    <t>PrimaryKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply_single_layer_terms </t>
+  </si>
+  <si>
+    <t>Ground-Up (GU)</t>
+  </si>
+  <si>
+    <t>ILW OCC Trigger</t>
+  </si>
+  <si>
+    <t>ILW AGG Trigger</t>
+  </si>
+  <si>
+    <t>ILW Prorata Trigger</t>
+  </si>
+  <si>
+    <t>OCCILW</t>
+  </si>
+  <si>
+    <t>Enable</t>
+  </si>
+  <si>
+    <t>Reinsurance Type Code</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer_type </t>
+  </si>
+  <si>
+    <t>Cacluate</t>
+  </si>
+  <si>
+    <t>Terms Used</t>
+  </si>
+  <si>
+    <t>Reinsurance Type Code Value</t>
+  </si>
+  <si>
+    <t>OCCTRIGGER</t>
+  </si>
+  <si>
+    <t>AGGTRIGGER</t>
+  </si>
+  <si>
+    <t>PRORATA</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>Fixed (Occ)</t>
+  </si>
+  <si>
+    <t>Enable (Occ/Agg)</t>
+  </si>
+  <si>
+    <t>Fixed (Agg)</t>
+  </si>
+  <si>
+    <t>("AGGXOL", "QS"):</t>
+  </si>
+  <si>
+    <t>calculate_agg_layer</t>
+  </si>
+  <si>
+    <t>AGGXOL / QS / GU</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OccurrenceLimit , OccurrenceRetention, Agg Limit, Agg Ret</t>
+  </si>
+  <si>
+    <t>Trigger Type</t>
+  </si>
+  <si>
+    <t>Hidden</t>
+  </si>
+  <si>
+    <t>Enable (Indemnity / Parametric / Index)</t>
+  </si>
+  <si>
+    <t>Disabled</t>
+  </si>
+  <si>
+    <t>("CATXOL", "RPP", "CATBOND", "FHCF")</t>
+  </si>
+  <si>
+    <t>calculate_occ_layer</t>
+  </si>
+  <si>
+    <t>CATXOL / CATBOND / FHCF / RPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OccurrenceLimit, OccurrenceRetention ,Agg Limit, Agg Ret</t>
+  </si>
+  <si>
+    <t>Trigger Type Value</t>
+  </si>
+  <si>
+    <t>Indemnity, Parametric, IndustryLoss</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis </t>
+  </si>
+  <si>
+    <t>("OCCTRIGGER")</t>
+  </si>
+  <si>
+    <t>calculate_ilw_occtrigger</t>
+  </si>
+  <si>
+    <t>ILW OCC TRIGGER</t>
+  </si>
+  <si>
+    <t>OccurrenceLimit,PrincipalAmount</t>
+  </si>
+  <si>
+    <t>("AGGTRIGGER")</t>
+  </si>
+  <si>
+    <t>calculate_ilw_aggtrigger</t>
+  </si>
+  <si>
+    <t>ILW AGG TRIGGER</t>
+  </si>
+  <si>
+    <t>Agg Limit,PrincipalAmount</t>
+  </si>
+  <si>
+    <t>Loss Basis Value</t>
+  </si>
+  <si>
+    <t>RiskAttaching, LossOccurring</t>
+  </si>
+  <si>
+    <t>PerOccurrence or AnnualAggregate</t>
+  </si>
+  <si>
+    <t>Attachment / Loss Structure</t>
+  </si>
+  <si>
+    <t>Inception Date</t>
+  </si>
+  <si>
+    <t>("PRORATA","OCCILW")</t>
+  </si>
+  <si>
+    <t>calculate_ilw_prorata</t>
+  </si>
+  <si>
+    <t>ILW PRORATA TRIGGER/ OCCILW</t>
+  </si>
+  <si>
+    <t>Agg Limit or PrincipalAmount</t>
+  </si>
+  <si>
+    <t>Expiration Date</t>
+  </si>
+  <si>
+    <t>Occurrence Retention</t>
+  </si>
+  <si>
+    <t>Fixed (0)</t>
+  </si>
+  <si>
+    <t>Conditional</t>
+  </si>
+  <si>
+    <t>Occ Limit</t>
+  </si>
+  <si>
+    <t>OuterAggregateDeductible</t>
+  </si>
+  <si>
+    <t>apply_agg_terms</t>
+  </si>
+  <si>
+    <t>Aggregate Retention</t>
+  </si>
+  <si>
+    <t>Match Loss</t>
+  </si>
+  <si>
+    <t>Occ Attach</t>
+  </si>
+  <si>
+    <t>FranchiseDeductible</t>
+  </si>
+  <si>
+    <t>apply_franchise_deductible</t>
+  </si>
+  <si>
+    <t>Deductible Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OuterAggregateDeductible / Franchise Deductible</t>
+  </si>
+  <si>
+    <t>apply_occ_terms</t>
+  </si>
+  <si>
+    <t>(yelt, occurrence_retention, occurrence_limit)</t>
+  </si>
+  <si>
+    <t>Principal Amount</t>
+  </si>
+  <si>
+    <t>Share / Participation</t>
+  </si>
+  <si>
+    <t>InuringOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply_agg_terms </t>
+  </si>
+  <si>
+    <t>(yelt, aggregate_retention, aggregate_limit)</t>
+  </si>
+  <si>
+    <t>% Placed</t>
+  </si>
+  <si>
+    <t>%Placed</t>
+  </si>
+  <si>
+    <t>Rate on Line (ROL)</t>
+  </si>
+  <si>
+    <t>Co-Ins</t>
+  </si>
+  <si>
+    <t>Reinstatement Count</t>
+  </si>
+  <si>
+    <t>PercentAnnualSpread  (ROL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CATXOL / CATBOND / FHCF / RPP</t>
+  </si>
+  <si>
+    <t>ROL%</t>
+  </si>
+  <si>
+    <t>CompanyLoss Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculate_occ_layer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">occ_limit, occ_retention , agg_limit , agg_retention </t>
+  </si>
+  <si>
+    <t>CompanyLossMax</t>
+  </si>
+  <si>
+    <t>Nth-event trigger</t>
+  </si>
+  <si>
+    <t>(StartingEventNumber, OccurrenceLimit) or OuterAggregateDeductible</t>
+  </si>
+  <si>
+    <t>IndustryLoss Minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   rip     </t>
+  </si>
+  <si>
+    <t>ReinstatementPremium, occ_limit</t>
+  </si>
+  <si>
+    <t>InvestmentAmount</t>
+  </si>
+  <si>
+    <t>IndustryLoss Maximum</t>
+  </si>
+  <si>
+    <t>Loss Thresholds</t>
+  </si>
+  <si>
+    <t>ReinstatementRate</t>
+  </si>
+  <si>
+    <t>yelt, OccurrenceLimit , OccurrenceRetention, Agg Limit, Agg Ret</t>
+  </si>
+  <si>
+    <t>Investment Amount</t>
+  </si>
+  <si>
+    <t>CompanyLoss Max</t>
+  </si>
+  <si>
+    <t>ILW Functions — Occurrence Trigger, Aggregate Trigger, Pro-Rata</t>
+  </si>
+  <si>
+    <t>AppliesToEvents</t>
+  </si>
+  <si>
+    <t>AppliedToAreas</t>
+  </si>
+  <si>
+    <t>AggregateLimit,PrincipalAmount</t>
+  </si>
+  <si>
+    <t>AggregateLimit or PrincipalAmount</t>
+  </si>
+  <si>
+    <t>Cashflow / Spread</t>
+  </si>
+  <si>
+    <t>StartingEvent#</t>
+  </si>
+  <si>
+    <t>LossSetAssociation</t>
+  </si>
+  <si>
+    <t>Franchise Deductible</t>
+  </si>
+  <si>
+    <t>AnnualSpreadPercent</t>
+  </si>
+  <si>
+    <t>(yelt, franchise_deductible):</t>
+  </si>
+  <si>
+    <t>RIP</t>
+  </si>
+  <si>
+    <t>Not Needed</t>
+  </si>
+  <si>
+    <t>get_rip_df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reinstatement_premium ("1@100,2@50" / "12" / "12%" / None) , occurrence_limit </t>
+  </si>
+  <si>
+    <t>Need to check the input format for reinstatement Premium</t>
+  </si>
+  <si>
+    <t>Applicability &amp; Scope</t>
+  </si>
+  <si>
+    <t>Not userinput</t>
+  </si>
+  <si>
+    <t>AppliedToAreas &amp; CededShare</t>
+  </si>
+  <si>
+    <t>isSeasonal</t>
+  </si>
+  <si>
+    <t>hasRIP (1 or 0)</t>
+  </si>
+  <si>
+    <t>isRPP</t>
+  </si>
+  <si>
+    <t>InnuringOrder</t>
+  </si>
 </sst>
 </file>
 
@@ -10931,7 +11392,7 @@
     <numFmt numFmtId="168" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="66">
+  <fonts count="72">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11400,8 +11861,48 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11501,6 +12002,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -12397,7 +12940,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="591">
+  <cellXfs count="673">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -13218,6 +13761,45 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="6"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -13251,46 +13833,10 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13313,6 +13859,18 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -13365,18 +13923,6 @@
     <xf numFmtId="164" fontId="18" fillId="10" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -13428,8 +13974,159 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="46" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="22" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="23" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="22" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="23" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -14579,14 +15276,8 @@
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>547</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -14595,7 +15286,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>547</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -14630,7 +15321,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>#REF!</c:v>
+                        <c:v>AggregateLimit</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -14640,7 +15331,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:numRef>
+                  <c:strRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -14648,47 +15339,40 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
+                    <c:strCache>
                       <c:ptCount val="12"/>
                       <c:pt idx="0">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>547</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>ILSInstrumentID</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>AggregateLimit</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>AggregateRetention</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>AnalysisSID</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>CedantName</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>CededAmount</c:v>
                       </c:pt>
                       <c:pt idx="9">
-                        <c:v>0</c:v>
+                        <c:v>CoinsuranceAmount</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>0</c:v>
+                        <c:v>CompanyLossMaximum</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>0</c:v>
+                        <c:v>CompanyLossMinimum</c:v>
                       </c:pt>
-                    </c:numCache>
-                  </c:numRef>
+                    </c:strCache>
+                  </c:strRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -23405,7 +24089,218 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>AggregateLimit</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>547</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>ILSInstrumentID</v>
+          </cell>
+          <cell r="B5">
+            <v>547</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>AggregateLimit</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>AggregateRetention</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>AnalysisSID</v>
+          </cell>
+          <cell r="B8">
+            <v>547</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>CedantName</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>NULL</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>CededAmount</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>NULL</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>CoinsuranceAmount</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>CompanyLossMaximum</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>CompanyLossMinimum</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="CAT Bond Pricing"/>
+      <sheetName val="LookUp"/>
+      <sheetName val="LossSetAssociation"/>
+      <sheetName val="AppliedToAreas&amp;Ceded%Share"/>
+      <sheetName val="AppliesToEvents"/>
+      <sheetName val="Meta Data"/>
+      <sheetName val="ILS Data"/>
+      <sheetName val="ILS Terms"/>
+      <sheetName val="rule"/>
+      <sheetName val="catBondResultYELT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>GU</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>QS</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>CATXOL</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>AGGXOL</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>AnnualAggregate</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>Parametric</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>PerOccurrence</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>Indemnity</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>LossOccuring</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>IndustryLoss</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>RiskAttaching</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>Yes. Match Losses to Maximum Occurrence Contribution</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>No. Do not match losses to the Maximum Occurrence Contribution</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>SubjectLayer</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>RetroSell</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>DropDown</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>Cascading</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>RPP</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>Innuring</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -24257,8 +25152,8 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="539"/>
-      <c r="O5" s="540"/>
+      <c r="N5" s="524"/>
+      <c r="O5" s="525"/>
       <c r="V5" s="42"/>
     </row>
     <row r="6" spans="2:22">
@@ -24296,10 +25191,10 @@
       <c r="M6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="541" t="s">
+      <c r="N6" s="526" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="541"/>
+      <c r="O6" s="526"/>
       <c r="V6" s="42"/>
     </row>
     <row r="7" spans="2:22">
@@ -24337,10 +25232,10 @@
       <c r="M7" s="11">
         <v>50000000</v>
       </c>
-      <c r="N7" s="542" t="s">
+      <c r="N7" s="521" t="s">
         <v>19</v>
       </c>
-      <c r="O7" s="542"/>
+      <c r="O7" s="521"/>
       <c r="V7" s="42"/>
     </row>
     <row r="8" spans="2:22">
@@ -24378,10 +25273,10 @@
       <c r="M8" s="11">
         <v>150000000</v>
       </c>
-      <c r="N8" s="542" t="s">
+      <c r="N8" s="521" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="542"/>
+      <c r="O8" s="521"/>
       <c r="V8" s="42"/>
     </row>
     <row r="9" spans="2:22">
@@ -24417,10 +25312,10 @@
       <c r="M9" s="11">
         <v>50000000</v>
       </c>
-      <c r="N9" s="542" t="s">
+      <c r="N9" s="521" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="542"/>
+      <c r="O9" s="521"/>
       <c r="V9" s="42"/>
     </row>
     <row r="10" spans="2:22">
@@ -24458,10 +25353,10 @@
       <c r="M10" s="11">
         <v>120000000</v>
       </c>
-      <c r="N10" s="542" t="s">
+      <c r="N10" s="521" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="542"/>
+      <c r="O10" s="521"/>
       <c r="V10" s="42"/>
     </row>
     <row r="11" spans="2:22">
@@ -24499,10 +25394,10 @@
       <c r="M11" s="11">
         <v>50000000</v>
       </c>
-      <c r="N11" s="542" t="s">
+      <c r="N11" s="521" t="s">
         <v>32</v>
       </c>
-      <c r="O11" s="542"/>
+      <c r="O11" s="521"/>
       <c r="V11" s="42"/>
     </row>
     <row r="12" spans="2:22">
@@ -24540,10 +25435,10 @@
       <c r="M12" s="11">
         <v>50000000</v>
       </c>
-      <c r="N12" s="542" t="s">
+      <c r="N12" s="521" t="s">
         <v>32</v>
       </c>
-      <c r="O12" s="542"/>
+      <c r="O12" s="521"/>
       <c r="V12" s="42"/>
     </row>
     <row r="13" spans="2:22">
@@ -24581,10 +25476,10 @@
       <c r="M13" s="11">
         <v>30000000</v>
       </c>
-      <c r="N13" s="542" t="s">
+      <c r="N13" s="521" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="542"/>
+      <c r="O13" s="521"/>
       <c r="V13" s="42"/>
     </row>
     <row r="14" spans="2:22" ht="15" thickBot="1">
@@ -24600,8 +25495,8 @@
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
-      <c r="N14" s="543"/>
-      <c r="O14" s="544"/>
+      <c r="N14" s="522"/>
+      <c r="O14" s="523"/>
       <c r="V14" s="42"/>
     </row>
     <row r="15" spans="2:22" ht="15" thickBot="1">
@@ -24655,19 +25550,19 @@
       <c r="B18" s="92">
         <v>2</v>
       </c>
-      <c r="C18" s="520" t="s">
+      <c r="C18" s="533" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="521"/>
+      <c r="D18" s="534"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="92">
         <v>3</v>
       </c>
-      <c r="L18" s="520" t="s">
+      <c r="L18" s="533" t="s">
         <v>86</v>
       </c>
-      <c r="M18" s="521"/>
+      <c r="M18" s="534"/>
       <c r="V18" s="42"/>
     </row>
     <row r="19" spans="2:22">
@@ -24736,15 +25631,15 @@
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="41"/>
-      <c r="M22" s="522" t="s">
+      <c r="M22" s="535" t="s">
         <v>85</v>
       </c>
-      <c r="N22" s="523"/>
-      <c r="O22" s="523"/>
-      <c r="P22" s="523"/>
-      <c r="Q22" s="523"/>
-      <c r="R22" s="523"/>
-      <c r="S22" s="524"/>
+      <c r="N22" s="536"/>
+      <c r="O22" s="536"/>
+      <c r="P22" s="536"/>
+      <c r="Q22" s="536"/>
+      <c r="R22" s="536"/>
+      <c r="S22" s="537"/>
       <c r="U22" s="42"/>
       <c r="V22" s="42"/>
     </row>
@@ -24755,13 +25650,13 @@
       <c r="J23" s="17"/>
       <c r="K23" s="11"/>
       <c r="L23" s="41"/>
-      <c r="M23" s="525"/>
-      <c r="N23" s="526"/>
-      <c r="O23" s="526"/>
-      <c r="P23" s="526"/>
-      <c r="Q23" s="526"/>
-      <c r="R23" s="526"/>
-      <c r="S23" s="527"/>
+      <c r="M23" s="538"/>
+      <c r="N23" s="539"/>
+      <c r="O23" s="539"/>
+      <c r="P23" s="539"/>
+      <c r="Q23" s="539"/>
+      <c r="R23" s="539"/>
+      <c r="S23" s="540"/>
       <c r="U23" s="42"/>
       <c r="V23" s="42"/>
     </row>
@@ -24783,13 +25678,13 @@
       <c r="J24" s="16"/>
       <c r="K24" s="11"/>
       <c r="L24" s="41"/>
-      <c r="M24" s="525"/>
-      <c r="N24" s="526"/>
-      <c r="O24" s="526"/>
-      <c r="P24" s="526"/>
-      <c r="Q24" s="526"/>
-      <c r="R24" s="526"/>
-      <c r="S24" s="527"/>
+      <c r="M24" s="538"/>
+      <c r="N24" s="539"/>
+      <c r="O24" s="539"/>
+      <c r="P24" s="539"/>
+      <c r="Q24" s="539"/>
+      <c r="R24" s="539"/>
+      <c r="S24" s="540"/>
       <c r="U24" s="42"/>
       <c r="V24" s="42"/>
     </row>
@@ -24800,13 +25695,13 @@
       <c r="J25" s="17"/>
       <c r="K25" s="11"/>
       <c r="L25" s="41"/>
-      <c r="M25" s="525"/>
-      <c r="N25" s="526"/>
-      <c r="O25" s="526"/>
-      <c r="P25" s="526"/>
-      <c r="Q25" s="526"/>
-      <c r="R25" s="526"/>
-      <c r="S25" s="527"/>
+      <c r="M25" s="538"/>
+      <c r="N25" s="539"/>
+      <c r="O25" s="539"/>
+      <c r="P25" s="539"/>
+      <c r="Q25" s="539"/>
+      <c r="R25" s="539"/>
+      <c r="S25" s="540"/>
       <c r="U25" s="42"/>
       <c r="V25" s="42"/>
     </row>
@@ -24820,13 +25715,13 @@
       <c r="J26" s="17"/>
       <c r="K26" s="11"/>
       <c r="L26" s="41"/>
-      <c r="M26" s="528"/>
-      <c r="N26" s="529"/>
-      <c r="O26" s="529"/>
-      <c r="P26" s="529"/>
-      <c r="Q26" s="529"/>
-      <c r="R26" s="529"/>
-      <c r="S26" s="530"/>
+      <c r="M26" s="541"/>
+      <c r="N26" s="542"/>
+      <c r="O26" s="542"/>
+      <c r="P26" s="542"/>
+      <c r="Q26" s="542"/>
+      <c r="R26" s="542"/>
+      <c r="S26" s="543"/>
       <c r="U26" s="42"/>
       <c r="V26" s="42"/>
     </row>
@@ -25276,18 +26171,18 @@
       <c r="B42" s="92">
         <v>4</v>
       </c>
-      <c r="C42" s="520" t="s">
+      <c r="C42" s="533" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="521"/>
+      <c r="D42" s="534"/>
       <c r="I42" s="11"/>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
       <c r="L42"/>
-      <c r="M42" s="534" t="s">
+      <c r="M42" s="528" t="s">
         <v>109</v>
       </c>
-      <c r="N42" s="535"/>
+      <c r="N42" s="529"/>
       <c r="O42" s="46"/>
       <c r="P42" s="22"/>
       <c r="Q42" s="23"/>
@@ -25392,24 +26287,24 @@
     </row>
     <row r="47" spans="2:22">
       <c r="B47" s="45"/>
-      <c r="C47" s="536" t="s">
+      <c r="C47" s="530" t="s">
         <v>105</v>
       </c>
-      <c r="D47" s="537"/>
-      <c r="E47" s="538" t="s">
+      <c r="D47" s="531"/>
+      <c r="E47" s="532" t="s">
         <v>106</v>
       </c>
-      <c r="F47" s="538"/>
-      <c r="G47" s="537" t="s">
+      <c r="F47" s="532"/>
+      <c r="G47" s="531" t="s">
         <v>107</v>
       </c>
-      <c r="H47" s="537"/>
+      <c r="H47" s="531"/>
       <c r="I47" s="40"/>
       <c r="J47" s="11"/>
-      <c r="K47" s="532" t="s">
+      <c r="K47" s="544" t="s">
         <v>107</v>
       </c>
-      <c r="L47" s="532"/>
+      <c r="L47" s="544"/>
       <c r="M47" s="23"/>
       <c r="N47" s="22"/>
       <c r="O47" s="46"/>
@@ -25441,10 +26336,10 @@
     </row>
     <row r="49" spans="2:22" s="22" customFormat="1" ht="15" thickBot="1">
       <c r="B49" s="79"/>
-      <c r="C49" s="534" t="s">
+      <c r="C49" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="535"/>
+      <c r="D49" s="529"/>
       <c r="E49" s="66" t="s">
         <v>67</v>
       </c>
@@ -25459,10 +26354,10 @@
       </c>
       <c r="I49" s="69"/>
       <c r="J49" s="60"/>
-      <c r="K49" s="533" t="s">
+      <c r="K49" s="545" t="s">
         <v>7</v>
       </c>
-      <c r="L49" s="533"/>
+      <c r="L49" s="545"/>
       <c r="M49" s="66" t="s">
         <v>67</v>
       </c>
@@ -25479,10 +26374,10 @@
     </row>
     <row r="50" spans="2:22" ht="15" thickBot="1">
       <c r="B50" s="45"/>
-      <c r="C50" s="531" t="s">
+      <c r="C50" s="527" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="531"/>
+      <c r="D50" s="527"/>
       <c r="E50" s="64" t="s">
         <v>76</v>
       </c>
@@ -25493,10 +26388,10 @@
       <c r="H50" s="21"/>
       <c r="I50" s="68"/>
       <c r="J50" s="11"/>
-      <c r="K50" s="531" t="s">
+      <c r="K50" s="527" t="s">
         <v>100</v>
       </c>
-      <c r="L50" s="531"/>
+      <c r="L50" s="527"/>
       <c r="M50" s="64" t="s">
         <v>76</v>
       </c>
@@ -25505,10 +26400,10 @@
     </row>
     <row r="51" spans="2:22" ht="15" thickBot="1">
       <c r="B51" s="45"/>
-      <c r="C51" s="531" t="s">
+      <c r="C51" s="527" t="s">
         <v>101</v>
       </c>
-      <c r="D51" s="531"/>
+      <c r="D51" s="527"/>
       <c r="E51" s="64" t="s">
         <v>77</v>
       </c>
@@ -25519,10 +26414,10 @@
       <c r="H51" s="21"/>
       <c r="I51" s="68"/>
       <c r="J51" s="11"/>
-      <c r="K51" s="531" t="s">
+      <c r="K51" s="527" t="s">
         <v>101</v>
       </c>
-      <c r="L51" s="531"/>
+      <c r="L51" s="527"/>
       <c r="M51" s="64" t="s">
         <v>77</v>
       </c>
@@ -25531,10 +26426,10 @@
     </row>
     <row r="52" spans="2:22" ht="15" thickBot="1">
       <c r="B52" s="45"/>
-      <c r="C52" s="531" t="s">
+      <c r="C52" s="527" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="531"/>
+      <c r="D52" s="527"/>
       <c r="E52" s="64" t="s">
         <v>78</v>
       </c>
@@ -25545,10 +26440,10 @@
       <c r="H52" s="21"/>
       <c r="I52" s="68"/>
       <c r="J52" s="11"/>
-      <c r="K52" s="531" t="s">
+      <c r="K52" s="527" t="s">
         <v>102</v>
       </c>
-      <c r="L52" s="531"/>
+      <c r="L52" s="527"/>
       <c r="M52" s="64" t="s">
         <v>78</v>
       </c>
@@ -25557,10 +26452,10 @@
     </row>
     <row r="53" spans="2:22" ht="15" thickBot="1">
       <c r="B53" s="45"/>
-      <c r="C53" s="531" t="s">
+      <c r="C53" s="527" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="531"/>
+      <c r="D53" s="527"/>
       <c r="E53" s="64" t="s">
         <v>79</v>
       </c>
@@ -25571,10 +26466,10 @@
       <c r="H53" s="21"/>
       <c r="I53" s="68"/>
       <c r="J53" s="11"/>
-      <c r="K53" s="531" t="s">
+      <c r="K53" s="527" t="s">
         <v>103</v>
       </c>
-      <c r="L53" s="531"/>
+      <c r="L53" s="527"/>
       <c r="M53" s="64" t="s">
         <v>79</v>
       </c>
@@ -25659,16 +26554,14 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="M22:S26"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
     <mergeCell ref="K52:L52"/>
     <mergeCell ref="K53:L53"/>
     <mergeCell ref="M42:N42"/>
@@ -25680,14 +26573,16 @@
     <mergeCell ref="G47:H47"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="K51:L51"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="M22:S26"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -27081,17 +27976,17 @@
       <c r="C195" s="101" t="s">
         <v>907</v>
       </c>
-      <c r="E195" s="574" t="s">
+      <c r="E195" s="575" t="s">
         <v>766</v>
       </c>
-      <c r="F195" s="574"/>
-      <c r="G195" s="574"/>
-      <c r="H195" s="574"/>
-      <c r="I195" s="574"/>
-      <c r="J195" s="574"/>
-      <c r="K195" s="574"/>
-      <c r="L195" s="574"/>
-      <c r="M195" s="574"/>
+      <c r="F195" s="575"/>
+      <c r="G195" s="575"/>
+      <c r="H195" s="575"/>
+      <c r="I195" s="575"/>
+      <c r="J195" s="575"/>
+      <c r="K195" s="575"/>
+      <c r="L195" s="575"/>
+      <c r="M195" s="575"/>
       <c r="N195" t="s">
         <v>767</v>
       </c>
@@ -27776,14 +28671,14 @@
       </c>
     </row>
     <row r="11" spans="2:25" ht="15.6">
-      <c r="B11" s="576" t="s">
+      <c r="B11" s="577" t="s">
         <v>1069</v>
       </c>
-      <c r="C11" s="576"/>
-      <c r="F11" s="576" t="s">
+      <c r="C11" s="577"/>
+      <c r="F11" s="577" t="s">
         <v>1070</v>
       </c>
-      <c r="G11" s="576"/>
+      <c r="G11" s="577"/>
     </row>
     <row r="12" spans="2:25" ht="15" thickBot="1">
       <c r="B12" s="3" t="s">
@@ -28506,10 +29401,10 @@
       </c>
     </row>
     <row r="36" spans="2:5" ht="21">
-      <c r="B36" s="575" t="s">
+      <c r="B36" s="576" t="s">
         <v>316</v>
       </c>
-      <c r="C36" s="575"/>
+      <c r="C36" s="576"/>
     </row>
     <row r="37" spans="2:5">
       <c r="C37" t="s">
@@ -41077,7 +41972,7 @@
       <c r="F17" s="127"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="577" t="s">
+      <c r="J17" s="578" t="s">
         <v>1014</v>
       </c>
       <c r="K17" s="346"/>
@@ -41101,7 +41996,7 @@
       <c r="F18" s="127"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="578"/>
+      <c r="J18" s="579"/>
       <c r="K18" s="344" t="s">
         <v>1015</v>
       </c>
@@ -41581,10 +42476,10 @@
       </c>
       <c r="F33" s="127"/>
       <c r="H33" s="10"/>
-      <c r="K33" s="579" t="s">
+      <c r="K33" s="580" t="s">
         <v>1031</v>
       </c>
-      <c r="N33" s="579" t="s">
+      <c r="N33" s="580" t="s">
         <v>833</v>
       </c>
       <c r="S33" s="101"/>
@@ -41605,8 +42500,8 @@
       </c>
       <c r="F34" s="127"/>
       <c r="H34" s="10"/>
-      <c r="K34" s="580"/>
-      <c r="N34" s="580"/>
+      <c r="K34" s="581"/>
+      <c r="N34" s="581"/>
       <c r="S34" s="101"/>
     </row>
     <row r="35" spans="1:21" ht="15" thickBot="1">
@@ -41625,8 +42520,8 @@
       </c>
       <c r="F35" s="127"/>
       <c r="H35" s="10"/>
-      <c r="K35" s="581"/>
-      <c r="N35" s="581"/>
+      <c r="K35" s="582"/>
+      <c r="N35" s="582"/>
       <c r="S35" s="101"/>
     </row>
     <row r="36" spans="1:21" ht="15" thickBot="1">
@@ -43943,22 +44838,22 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="100"/>
-      <c r="F1" s="582" t="s">
+      <c r="F1" s="583" t="s">
         <v>1477</v>
       </c>
-      <c r="G1" s="583"/>
-      <c r="H1" s="583"/>
-      <c r="I1" s="583"/>
-      <c r="J1" s="584"/>
-      <c r="K1" s="585" t="s">
+      <c r="G1" s="584"/>
+      <c r="H1" s="584"/>
+      <c r="I1" s="584"/>
+      <c r="J1" s="585"/>
+      <c r="K1" s="586" t="s">
         <v>1476</v>
       </c>
-      <c r="L1" s="586"/>
-      <c r="M1" s="587" t="s">
+      <c r="L1" s="587"/>
+      <c r="M1" s="588" t="s">
         <v>1433</v>
       </c>
-      <c r="N1" s="588"/>
-      <c r="O1" s="589"/>
+      <c r="N1" s="589"/>
+      <c r="O1" s="590"/>
       <c r="T1" s="3" t="s">
         <v>1469</v>
       </c>
@@ -44937,20 +45832,20 @@
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1"/>
     <row r="3" spans="1:2" ht="21.6" thickBot="1">
-      <c r="A3" s="545" t="s">
+      <c r="A3" s="546" t="s">
         <v>2386</v>
       </c>
-      <c r="B3" s="546"/>
+      <c r="B3" s="547"/>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1">
-      <c r="A4" s="547" t="s">
+      <c r="A4" s="548" t="s">
         <v>2387</v>
       </c>
-      <c r="B4" s="548"/>
+      <c r="B4" s="549"/>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1">
-      <c r="A5" s="549"/>
-      <c r="B5" s="550"/>
+      <c r="A5" s="550"/>
+      <c r="B5" s="551"/>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1">
       <c r="A6" s="472" t="s">
@@ -45092,50 +45987,50 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="551" t="s">
+      <c r="A28" s="552" t="s">
         <v>2405</v>
       </c>
-      <c r="B28" s="551"/>
-      <c r="C28" s="551"/>
-      <c r="D28" s="551"/>
-      <c r="E28" s="551"/>
-      <c r="F28" s="551"/>
-      <c r="G28" s="551"/>
-      <c r="H28" s="551"/>
-      <c r="I28" s="551"/>
+      <c r="B28" s="552"/>
+      <c r="C28" s="552"/>
+      <c r="D28" s="552"/>
+      <c r="E28" s="552"/>
+      <c r="F28" s="552"/>
+      <c r="G28" s="552"/>
+      <c r="H28" s="552"/>
+      <c r="I28" s="552"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="551"/>
-      <c r="B29" s="551"/>
-      <c r="C29" s="551"/>
-      <c r="D29" s="551"/>
-      <c r="E29" s="551"/>
-      <c r="F29" s="551"/>
-      <c r="G29" s="551"/>
-      <c r="H29" s="551"/>
-      <c r="I29" s="551"/>
+      <c r="A29" s="552"/>
+      <c r="B29" s="552"/>
+      <c r="C29" s="552"/>
+      <c r="D29" s="552"/>
+      <c r="E29" s="552"/>
+      <c r="F29" s="552"/>
+      <c r="G29" s="552"/>
+      <c r="H29" s="552"/>
+      <c r="I29" s="552"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="551"/>
-      <c r="B30" s="551"/>
-      <c r="C30" s="551"/>
-      <c r="D30" s="551"/>
-      <c r="E30" s="551"/>
-      <c r="F30" s="551"/>
-      <c r="G30" s="551"/>
-      <c r="H30" s="551"/>
-      <c r="I30" s="551"/>
+      <c r="A30" s="552"/>
+      <c r="B30" s="552"/>
+      <c r="C30" s="552"/>
+      <c r="D30" s="552"/>
+      <c r="E30" s="552"/>
+      <c r="F30" s="552"/>
+      <c r="G30" s="552"/>
+      <c r="H30" s="552"/>
+      <c r="I30" s="552"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="551"/>
-      <c r="B31" s="551"/>
-      <c r="C31" s="551"/>
-      <c r="D31" s="551"/>
-      <c r="E31" s="551"/>
-      <c r="F31" s="551"/>
-      <c r="G31" s="551"/>
-      <c r="H31" s="551"/>
-      <c r="I31" s="551"/>
+      <c r="A31" s="552"/>
+      <c r="B31" s="552"/>
+      <c r="C31" s="552"/>
+      <c r="D31" s="552"/>
+      <c r="E31" s="552"/>
+      <c r="F31" s="552"/>
+      <c r="G31" s="552"/>
+      <c r="H31" s="552"/>
+      <c r="I31" s="552"/>
     </row>
     <row r="33" spans="1:14" ht="15.6">
       <c r="A33" s="483" t="s">
@@ -63456,16 +64351,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="590" t="s">
+      <c r="A1" s="520" t="s">
         <v>1144</v>
       </c>
-      <c r="B1" s="590" t="s">
+      <c r="B1" s="520" t="s">
         <v>2602</v>
       </c>
-      <c r="C1" s="590" t="s">
+      <c r="C1" s="520" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="590" t="s">
+      <c r="D1" s="520" t="s">
         <v>2603</v>
       </c>
     </row>
@@ -63747,6 +64642,1938 @@
       </c>
       <c r="D21" s="318" t="s">
         <v>2631</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28E8C23-274B-460F-BABB-F0E0E9C79DBD}">
+  <sheetPr codeName="Sheet9"/>
+  <dimension ref="A1:AI47"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36.109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="15" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="51.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="24" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="24" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="0" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="32.109375" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="57.109375" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="31.33203125" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="53.21875" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.21875" customWidth="1"/>
+    <col min="26" max="26" width="13" customWidth="1"/>
+    <col min="27" max="27" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.33203125" customWidth="1"/>
+    <col min="29" max="29" width="17.109375" customWidth="1"/>
+    <col min="30" max="31" width="8.21875" customWidth="1"/>
+    <col min="32" max="32" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:35">
+      <c r="A1" s="3" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35">
+      <c r="A2" s="3"/>
+      <c r="K2" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" ht="18.600000000000001" thickBot="1">
+      <c r="A3" s="591" t="s">
+        <v>2634</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>2635</v>
+      </c>
+      <c r="O3" t="s">
+        <v>2636</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>2637</v>
+      </c>
+      <c r="X3" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" ht="29.4" thickBot="1">
+      <c r="A4" s="592" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B4" s="592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="592" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D4" s="592" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E4" s="592" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F4" s="592" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G4" s="592" t="s">
+        <v>2641</v>
+      </c>
+      <c r="J4" s="88"/>
+      <c r="K4" s="593" t="s">
+        <v>2642</v>
+      </c>
+      <c r="N4" s="367" t="s">
+        <v>2259</v>
+      </c>
+      <c r="O4" s="350" t="s">
+        <v>2643</v>
+      </c>
+      <c r="R4" s="594" t="s">
+        <v>2644</v>
+      </c>
+      <c r="X4" s="595" t="s">
+        <v>2639</v>
+      </c>
+      <c r="Y4" s="596" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z4" s="596" t="s">
+        <v>2645</v>
+      </c>
+      <c r="AA4" s="596" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AB4" s="596" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AC4" s="596" t="s">
+        <v>1373</v>
+      </c>
+      <c r="AD4" s="596" t="s">
+        <v>2641</v>
+      </c>
+      <c r="AE4" s="596" t="s">
+        <v>2055</v>
+      </c>
+      <c r="AF4" s="596" t="s">
+        <v>2646</v>
+      </c>
+      <c r="AG4" s="596" t="s">
+        <v>2647</v>
+      </c>
+      <c r="AH4" s="596" t="s">
+        <v>2648</v>
+      </c>
+      <c r="AI4" s="597" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="15" thickBot="1">
+      <c r="A5" s="318" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B5" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C5" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D5" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E5" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F5" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G5" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K5" s="599" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="368"/>
+      <c r="O5" s="349"/>
+      <c r="R5" s="600"/>
+      <c r="S5" s="600"/>
+      <c r="X5" s="601" t="s">
+        <v>2651</v>
+      </c>
+      <c r="Y5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AA5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AB5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AE5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AF5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AG5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AH5" s="602" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AI5" s="603" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" ht="36.6" customHeight="1" thickBot="1">
+      <c r="A6" s="318" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B6" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C6" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D6" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E6" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F6" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G6" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K6" s="604" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" s="368"/>
+      <c r="O6" s="349"/>
+      <c r="R6" s="594" t="s">
+        <v>2653</v>
+      </c>
+      <c r="S6" s="605" t="s">
+        <v>2654</v>
+      </c>
+      <c r="T6" s="606" t="s">
+        <v>2653</v>
+      </c>
+      <c r="U6" s="607" t="s">
+        <v>2655</v>
+      </c>
+      <c r="X6" s="608" t="s">
+        <v>2656</v>
+      </c>
+      <c r="Y6" s="609" t="s">
+        <v>2164</v>
+      </c>
+      <c r="Z6" s="609" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AA6" s="609" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AB6" s="609" t="s">
+        <v>2148</v>
+      </c>
+      <c r="AC6" s="609" t="s">
+        <v>2143</v>
+      </c>
+      <c r="AD6" s="609" t="s">
+        <v>2641</v>
+      </c>
+      <c r="AE6" s="609" t="s">
+        <v>2055</v>
+      </c>
+      <c r="AF6" s="609" t="s">
+        <v>2657</v>
+      </c>
+      <c r="AG6" s="609" t="s">
+        <v>2658</v>
+      </c>
+      <c r="AH6" s="609" t="s">
+        <v>2659</v>
+      </c>
+      <c r="AI6" s="610" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35">
+      <c r="A7" s="318" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B7" s="598" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C7" s="598" t="s">
+        <v>2661</v>
+      </c>
+      <c r="D7" s="598" t="s">
+        <v>2662</v>
+      </c>
+      <c r="E7" s="598" t="s">
+        <v>2661</v>
+      </c>
+      <c r="F7" s="598" t="s">
+        <v>2663</v>
+      </c>
+      <c r="G7" s="598" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K7" s="611" t="s">
+        <v>2181</v>
+      </c>
+      <c r="N7" s="368" t="s">
+        <v>2181</v>
+      </c>
+      <c r="O7" s="349"/>
+      <c r="R7" s="612" t="s">
+        <v>2664</v>
+      </c>
+      <c r="S7" s="613" t="s">
+        <v>2665</v>
+      </c>
+      <c r="T7" s="94" t="s">
+        <v>2666</v>
+      </c>
+      <c r="U7" s="614" t="s">
+        <v>2667</v>
+      </c>
+      <c r="X7" s="615" t="s">
+        <v>2668</v>
+      </c>
+      <c r="Y7" s="616" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z7" s="616" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA7" s="616" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB7" s="616" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AC7" s="616" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AD7" s="616" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE7" s="616" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AF7" s="616" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AG7" s="616" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AH7" s="616" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AI7" s="617" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35">
+      <c r="A8" s="318" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B8" s="598" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C8" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D8" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E8" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F8" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G8" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K8" s="618" t="s">
+        <v>1323</v>
+      </c>
+      <c r="N8" s="368"/>
+      <c r="O8" s="349"/>
+      <c r="R8" s="619" t="s">
+        <v>2672</v>
+      </c>
+      <c r="S8" s="620" t="s">
+        <v>2673</v>
+      </c>
+      <c r="T8" s="94" t="s">
+        <v>2674</v>
+      </c>
+      <c r="U8" s="621" t="s">
+        <v>2675</v>
+      </c>
+      <c r="X8" s="622" t="s">
+        <v>2676</v>
+      </c>
+      <c r="Y8" s="623" t="s">
+        <v>2677</v>
+      </c>
+      <c r="Z8" s="624" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AA8" s="624" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AB8" s="623" t="s">
+        <v>338</v>
+      </c>
+      <c r="AC8" s="623" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD8" s="623" t="s">
+        <v>338</v>
+      </c>
+      <c r="AE8" s="623" t="s">
+        <v>338</v>
+      </c>
+      <c r="AF8" s="623" t="s">
+        <v>2114</v>
+      </c>
+      <c r="AG8" s="623" t="s">
+        <v>2114</v>
+      </c>
+      <c r="AH8" s="623" t="s">
+        <v>2114</v>
+      </c>
+      <c r="AI8" s="625" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35">
+      <c r="A9" s="318" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B9" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C9" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D9" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E9" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F9" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G9" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K9" s="618" t="s">
+        <v>2679</v>
+      </c>
+      <c r="N9" s="368"/>
+      <c r="O9" s="349"/>
+      <c r="R9" s="619" t="s">
+        <v>2680</v>
+      </c>
+      <c r="S9" s="626" t="s">
+        <v>2681</v>
+      </c>
+      <c r="T9" s="94" t="s">
+        <v>2682</v>
+      </c>
+      <c r="U9" s="621" t="s">
+        <v>2683</v>
+      </c>
+      <c r="X9" s="664" t="s">
+        <v>2395</v>
+      </c>
+      <c r="Y9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z9" s="665" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AB9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AE9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AF9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AG9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AH9" s="665" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AI9" s="666" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" ht="15" thickBot="1">
+      <c r="K10" s="618" t="s">
+        <v>2298</v>
+      </c>
+      <c r="N10" s="368"/>
+      <c r="O10" s="349"/>
+      <c r="R10" s="619" t="s">
+        <v>2684</v>
+      </c>
+      <c r="S10" s="627" t="s">
+        <v>2685</v>
+      </c>
+      <c r="T10" s="94" t="s">
+        <v>2686</v>
+      </c>
+      <c r="U10" s="628" t="s">
+        <v>2687</v>
+      </c>
+      <c r="X10" s="667" t="s">
+        <v>2688</v>
+      </c>
+      <c r="Y10" s="668" t="s">
+        <v>2118</v>
+      </c>
+      <c r="Z10" s="668" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AA10" s="669" t="s">
+        <v>2689</v>
+      </c>
+      <c r="AB10" s="670" t="s">
+        <v>2118</v>
+      </c>
+      <c r="AC10" s="671" t="s">
+        <v>2124</v>
+      </c>
+      <c r="AD10" s="670" t="s">
+        <v>2118</v>
+      </c>
+      <c r="AE10" s="670" t="s">
+        <v>2118</v>
+      </c>
+      <c r="AF10" s="670" t="s">
+        <v>2118</v>
+      </c>
+      <c r="AG10" s="671" t="s">
+        <v>2124</v>
+      </c>
+      <c r="AH10" s="670" t="s">
+        <v>2690</v>
+      </c>
+      <c r="AI10" s="672" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" ht="18.600000000000001" thickBot="1">
+      <c r="A11" s="591" t="s">
+        <v>2691</v>
+      </c>
+      <c r="K11" s="629" t="s">
+        <v>2692</v>
+      </c>
+      <c r="N11" s="368" t="s">
+        <v>1076</v>
+      </c>
+      <c r="O11" s="349"/>
+      <c r="R11" s="630" t="s">
+        <v>2693</v>
+      </c>
+      <c r="S11" s="631" t="s">
+        <v>2694</v>
+      </c>
+      <c r="T11" s="632" t="s">
+        <v>2695</v>
+      </c>
+      <c r="U11" s="633" t="s">
+        <v>2696</v>
+      </c>
+      <c r="X11" s="634" t="s">
+        <v>1026</v>
+      </c>
+      <c r="Y11" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z11" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA11" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB11" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC11" s="635" t="s">
+        <v>662</v>
+      </c>
+      <c r="AD11" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AE11" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AF11" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AG11" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AH11" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AI11" s="636" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="15" thickBot="1">
+      <c r="A12" s="592" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B12" s="592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="592" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D12" s="592" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E12" s="592" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F12" s="592" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G12" s="592" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K12" s="637" t="s">
+        <v>2697</v>
+      </c>
+      <c r="N12" s="368" t="s">
+        <v>518</v>
+      </c>
+      <c r="O12" s="349"/>
+      <c r="X12" s="634" t="s">
+        <v>2698</v>
+      </c>
+      <c r="Y12" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z12" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA12" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB12" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC12" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AD12" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AE12" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AF12" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AG12" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AH12" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AI12" s="636" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" ht="15" thickBot="1">
+      <c r="A13" s="318" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B13" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C13" s="598" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D13" s="598" t="s">
+        <v>2699</v>
+      </c>
+      <c r="E13" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F13" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G13" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K13" s="637" t="s">
+        <v>2318</v>
+      </c>
+      <c r="N13" s="368" t="s">
+        <v>281</v>
+      </c>
+      <c r="O13" s="349"/>
+      <c r="R13" s="638" t="s">
+        <v>2254</v>
+      </c>
+      <c r="S13" s="605" t="s">
+        <v>2654</v>
+      </c>
+      <c r="X13" s="634" t="s">
+        <v>1398</v>
+      </c>
+      <c r="Y13" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="Z13" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA13" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB13" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AC13" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD13" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE13" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AF13" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AG13" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AH13" s="328" t="s">
+        <v>2700</v>
+      </c>
+      <c r="AI13" s="328" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="A14" s="318" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B14" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C14" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D14" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E14" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F14" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G14" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K14" s="637" t="s">
+        <v>2701</v>
+      </c>
+      <c r="N14" s="368" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="349"/>
+      <c r="R14" s="367" t="s">
+        <v>2702</v>
+      </c>
+      <c r="S14" s="639" t="s">
+        <v>2703</v>
+      </c>
+      <c r="X14" s="634" t="s">
+        <v>2704</v>
+      </c>
+      <c r="Y14" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="Z14" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA14" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB14" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AC14" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD14" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE14" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AF14" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AG14" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AH14" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AI14" s="328" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="15" thickBot="1">
+      <c r="A15" s="318" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B15" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C15" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D15" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E15" s="598" t="s">
+        <v>662</v>
+      </c>
+      <c r="F15" s="598" t="s">
+        <v>662</v>
+      </c>
+      <c r="G15" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K15" s="637" t="s">
+        <v>2706</v>
+      </c>
+      <c r="N15" s="368" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="349"/>
+      <c r="R15" s="640" t="s">
+        <v>2707</v>
+      </c>
+      <c r="S15" s="633" t="s">
+        <v>2708</v>
+      </c>
+      <c r="X15" s="657" t="s">
+        <v>1433</v>
+      </c>
+      <c r="Y15" s="658" t="s">
+        <v>662</v>
+      </c>
+      <c r="Z15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AC15" s="658" t="s">
+        <v>662</v>
+      </c>
+      <c r="AD15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AF15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AG15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AH15" s="658" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AI15" s="659" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" ht="15" thickBot="1">
+      <c r="A16" s="318" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B16" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C16" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D16" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E16" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F16" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G16" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K16" s="637" t="s">
+        <v>1467</v>
+      </c>
+      <c r="N16" s="368" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" s="349"/>
+      <c r="X16" s="660" t="s">
+        <v>2709</v>
+      </c>
+      <c r="Y16" s="661" t="s">
+        <v>2710</v>
+      </c>
+      <c r="Z16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AA16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AB16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AC16" s="661" t="s">
+        <v>2710</v>
+      </c>
+      <c r="AD16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AE16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AF16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AG16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AH16" s="662" t="s">
+        <v>2678</v>
+      </c>
+      <c r="AI16" s="663" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35">
+      <c r="K17" s="637" t="s">
+        <v>1466</v>
+      </c>
+      <c r="N17" s="368" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" s="349"/>
+      <c r="R17" s="367" t="s">
+        <v>2711</v>
+      </c>
+      <c r="S17" s="350" t="s">
+        <v>2712</v>
+      </c>
+      <c r="X17" s="634" t="s">
+        <v>2713</v>
+      </c>
+      <c r="Y17" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z17" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA17" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB17" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AC17" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AD17" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE17" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AF17" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AG17" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AH17" s="328" t="s">
+        <v>2700</v>
+      </c>
+      <c r="AI17" s="636" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" ht="18.600000000000001" thickBot="1">
+      <c r="A18" s="591" t="s">
+        <v>2714</v>
+      </c>
+      <c r="K18" s="641" t="s">
+        <v>2715</v>
+      </c>
+      <c r="N18" s="368" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O18" s="349"/>
+      <c r="R18" s="369" t="s">
+        <v>2716</v>
+      </c>
+      <c r="S18" s="370" t="s">
+        <v>2717</v>
+      </c>
+      <c r="X18" s="634" t="s">
+        <v>2718</v>
+      </c>
+      <c r="Y18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="Z18" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AB18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AE18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AF18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AG18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AH18" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AI18" s="636" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35">
+      <c r="A19" s="592" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B19" s="592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="592" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D19" s="592" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E19" s="592" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F19" s="592" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G19" s="592" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K19" s="629" t="s">
+        <v>2719</v>
+      </c>
+      <c r="N19" s="368"/>
+      <c r="O19" s="349"/>
+      <c r="X19" s="634" t="s">
+        <v>2720</v>
+      </c>
+      <c r="Y19" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="Z19" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA19" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB19" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC19" s="328" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD19" s="328" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE19" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AF19" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AG19" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AH19" s="328" t="s">
+        <v>662</v>
+      </c>
+      <c r="AI19" s="636" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" ht="15" thickBot="1">
+      <c r="A20" s="318" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B20" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C20" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D20" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E20" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F20" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G20" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K20" s="637" t="s">
+        <v>2721</v>
+      </c>
+      <c r="N20" s="368"/>
+      <c r="O20" s="349"/>
+      <c r="X20" s="642" t="s">
+        <v>2722</v>
+      </c>
+      <c r="Y20" s="643" t="s">
+        <v>662</v>
+      </c>
+      <c r="Z20" s="643" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AA20" s="643" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AB20" s="643" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AC20" s="643" t="s">
+        <v>662</v>
+      </c>
+      <c r="AD20" s="643" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AE20" s="643" t="s">
+        <v>662</v>
+      </c>
+      <c r="AF20" s="643" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AG20" s="643" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AH20" s="643" t="s">
+        <v>2669</v>
+      </c>
+      <c r="AI20" s="644" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" ht="15" thickBot="1">
+      <c r="A21" s="318" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B21" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C21" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D21" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E21" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F21" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G21" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K21" s="641" t="s">
+        <v>2723</v>
+      </c>
+      <c r="N21" s="368" t="s">
+        <v>2723</v>
+      </c>
+      <c r="O21" s="349"/>
+      <c r="R21" s="3" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35">
+      <c r="A22" s="318" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B22" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C22" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D22" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E22" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F22" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G22" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K22" s="629" t="s">
+        <v>2726</v>
+      </c>
+      <c r="N22" s="368"/>
+      <c r="O22" s="349"/>
+      <c r="R22" s="645" t="s">
+        <v>2727</v>
+      </c>
+      <c r="S22" s="646" t="s">
+        <v>2728</v>
+      </c>
+      <c r="X22" s="647"/>
+      <c r="Y22" s="647"/>
+    </row>
+    <row r="23" spans="1:35">
+      <c r="A23" s="318" t="s">
+        <v>526</v>
+      </c>
+      <c r="B23" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C23" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D23" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E23" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F23" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G23" s="98" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K23" s="637" t="s">
+        <v>2729</v>
+      </c>
+      <c r="N23" s="368"/>
+      <c r="O23" s="349"/>
+      <c r="R23" s="619" t="s">
+        <v>2730</v>
+      </c>
+      <c r="S23" s="628" t="s">
+        <v>2731</v>
+      </c>
+      <c r="X23" s="329"/>
+      <c r="Y23" s="329"/>
+    </row>
+    <row r="24" spans="1:35" ht="15" thickBot="1">
+      <c r="A24" s="318" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C24" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D24" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E24" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F24" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G24" s="98" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K24" s="637" t="s">
+        <v>2732</v>
+      </c>
+      <c r="N24" s="368"/>
+      <c r="O24" s="349"/>
+      <c r="R24" s="630" t="s">
+        <v>2733</v>
+      </c>
+      <c r="S24" s="633" t="s">
+        <v>2734</v>
+      </c>
+      <c r="X24" s="329"/>
+      <c r="Y24" s="329"/>
+    </row>
+    <row r="25" spans="1:35" ht="15" thickBot="1">
+      <c r="A25" s="318" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B25" s="598" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C25" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D25" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E25" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F25" s="598" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G25" s="98" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K25" s="641" t="s">
+        <v>2736</v>
+      </c>
+      <c r="N25" s="368"/>
+      <c r="O25" s="349"/>
+      <c r="X25" s="329"/>
+      <c r="Y25" s="329"/>
+    </row>
+    <row r="26" spans="1:35" ht="15" thickBot="1">
+      <c r="K26" s="629" t="s">
+        <v>555</v>
+      </c>
+      <c r="N26" s="368"/>
+      <c r="O26" s="349"/>
+      <c r="R26" s="3" t="s">
+        <v>2666</v>
+      </c>
+      <c r="X26" s="329"/>
+      <c r="Y26" s="329"/>
+    </row>
+    <row r="27" spans="1:35" ht="18.600000000000001" thickBot="1">
+      <c r="A27" s="591" t="s">
+        <v>2737</v>
+      </c>
+      <c r="K27" s="637" t="s">
+        <v>2738</v>
+      </c>
+      <c r="N27" s="368" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O27" s="349"/>
+      <c r="R27" s="648" t="s">
+        <v>2665</v>
+      </c>
+      <c r="S27" s="649" t="s">
+        <v>2739</v>
+      </c>
+      <c r="X27" s="329"/>
+      <c r="Y27" s="329"/>
+    </row>
+    <row r="28" spans="1:35">
+      <c r="A28" s="592" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B28" s="592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="592" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D28" s="592" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E28" s="592" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F28" s="592" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G28" s="592" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K28" s="593" t="s">
+        <v>2713</v>
+      </c>
+      <c r="N28" s="368"/>
+      <c r="O28" s="349"/>
+      <c r="X28" s="329"/>
+      <c r="Y28" s="329"/>
+    </row>
+    <row r="29" spans="1:35">
+      <c r="A29" s="328" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B29" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C29" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D29" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E29" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="F29" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="G29" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="K29" s="599" t="s">
+        <v>2740</v>
+      </c>
+      <c r="N29" s="368" t="s">
+        <v>42</v>
+      </c>
+      <c r="O29" s="349"/>
+      <c r="X29" s="329"/>
+      <c r="Y29" s="329"/>
+    </row>
+    <row r="30" spans="1:35" ht="15" thickBot="1">
+      <c r="A30" s="328" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B30" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C30" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D30" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E30" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="F30" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="G30" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="K30" s="599" t="s">
+        <v>526</v>
+      </c>
+      <c r="N30" s="368"/>
+      <c r="O30" s="349"/>
+      <c r="R30" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="X30" s="329"/>
+      <c r="Y30" s="329"/>
+    </row>
+    <row r="31" spans="1:35">
+      <c r="A31" s="328" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B31" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C31" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D31" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E31" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F31" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G31" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K31" s="629" t="s">
+        <v>2743</v>
+      </c>
+      <c r="N31" s="368" t="s">
+        <v>526</v>
+      </c>
+      <c r="O31" s="349"/>
+      <c r="R31" s="651" t="s">
+        <v>2681</v>
+      </c>
+      <c r="S31" s="646" t="s">
+        <v>2683</v>
+      </c>
+      <c r="X31" s="329"/>
+      <c r="Y31" s="329"/>
+    </row>
+    <row r="32" spans="1:35">
+      <c r="A32" s="328" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B32" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C32" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D32" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E32" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F32" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G32" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K32" s="637" t="s">
+        <v>2744</v>
+      </c>
+      <c r="N32" s="368"/>
+      <c r="O32" s="349"/>
+      <c r="R32" s="652" t="s">
+        <v>2685</v>
+      </c>
+      <c r="S32" s="628" t="s">
+        <v>2745</v>
+      </c>
+      <c r="X32" s="329"/>
+      <c r="Y32" s="329"/>
+    </row>
+    <row r="33" spans="1:25" ht="15" thickBot="1">
+      <c r="K33" s="637" t="s">
+        <v>187</v>
+      </c>
+      <c r="N33" s="368"/>
+      <c r="O33" s="349"/>
+      <c r="R33" s="653" t="s">
+        <v>2694</v>
+      </c>
+      <c r="S33" s="633" t="s">
+        <v>2746</v>
+      </c>
+      <c r="X33" s="329"/>
+      <c r="Y33" s="329"/>
+    </row>
+    <row r="34" spans="1:25" ht="18">
+      <c r="A34" s="591" t="s">
+        <v>2747</v>
+      </c>
+      <c r="K34" s="637" t="s">
+        <v>2748</v>
+      </c>
+      <c r="N34" s="368"/>
+      <c r="O34" s="349"/>
+      <c r="X34" s="329"/>
+      <c r="Y34" s="329"/>
+    </row>
+    <row r="35" spans="1:25" ht="15" thickBot="1">
+      <c r="A35" s="592" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B35" s="592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="592" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D35" s="592" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E35" s="592" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F35" s="592" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G35" s="592" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K35" s="637" t="s">
+        <v>2749</v>
+      </c>
+      <c r="N35" s="368"/>
+      <c r="O35" s="349"/>
+      <c r="R35" s="3" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="15" thickBot="1">
+      <c r="A36" s="328" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B36" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C36" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D36" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E36" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F36" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G36" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K36" s="629" t="s">
+        <v>2254</v>
+      </c>
+      <c r="N36" s="368" t="s">
+        <v>1328</v>
+      </c>
+      <c r="O36" s="349"/>
+      <c r="R36" s="19" t="s">
+        <v>2708</v>
+      </c>
+      <c r="S36" s="649" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="15" thickBot="1">
+      <c r="A37" s="328" t="s">
+        <v>555</v>
+      </c>
+      <c r="B37" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C37" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D37" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E37" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F37" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G37" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="K37" s="641" t="s">
+        <v>1433</v>
+      </c>
+      <c r="N37" s="368"/>
+      <c r="O37" s="349"/>
+    </row>
+    <row r="38" spans="1:25" ht="15" thickBot="1">
+      <c r="A38" s="328" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B38" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C38" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D38" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E38" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F38" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G38" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="N38" s="368" t="s">
+        <v>2254</v>
+      </c>
+      <c r="P38" s="654"/>
+      <c r="R38" s="3" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="15" thickBot="1">
+      <c r="N39" s="368" t="s">
+        <v>2249</v>
+      </c>
+      <c r="O39" s="349" t="s">
+        <v>2754</v>
+      </c>
+      <c r="R39" s="19" t="s">
+        <v>2755</v>
+      </c>
+      <c r="S39" s="649" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="N40" s="368" t="s">
+        <v>2320</v>
+      </c>
+      <c r="O40" s="349" t="s">
+        <v>2754</v>
+      </c>
+      <c r="R40" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="18">
+      <c r="A41" s="591" t="s">
+        <v>2758</v>
+      </c>
+      <c r="N41" s="655" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O41" s="349" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="A42" s="592" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B42" s="592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="592" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D42" s="592" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E42" s="592" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F42" s="592" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G42" s="592" t="s">
+        <v>2641</v>
+      </c>
+      <c r="N42" s="655" t="s">
+        <v>1325</v>
+      </c>
+      <c r="O42" s="349" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" s="328" t="s">
+        <v>2760</v>
+      </c>
+      <c r="B43" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C43" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D43" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E43" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F43" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G43" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="N43" s="655" t="s">
+        <v>2761</v>
+      </c>
+      <c r="O43" s="349" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="A44" s="328" t="s">
+        <v>2743</v>
+      </c>
+      <c r="B44" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C44" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D44" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E44" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F44" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G44" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="N44" s="655" t="s">
+        <v>2762</v>
+      </c>
+      <c r="O44" s="349" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="15" thickBot="1">
+      <c r="A45" s="328" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C45" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D45" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E45" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F45" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G45" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="N45" s="656" t="s">
+        <v>2763</v>
+      </c>
+      <c r="O45" s="370" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="A46" s="328" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B46" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C46" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D46" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E46" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="F46" s="650" t="s">
+        <v>662</v>
+      </c>
+      <c r="G46" s="650" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
+      <c r="A47" s="328" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B47" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C47" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D47" s="650" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E47" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F47" s="650" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G47" s="650" t="s">
+        <v>2650</v>
       </c>
     </row>
   </sheetData>
@@ -65578,10 +68405,10 @@
       <c r="B108" s="126">
         <v>1</v>
       </c>
-      <c r="C108" s="556" t="s">
+      <c r="C108" s="561" t="s">
         <v>45</v>
       </c>
-      <c r="D108" s="557"/>
+      <c r="D108" s="562"/>
       <c r="E108" s="127"/>
       <c r="F108" s="127"/>
       <c r="G108" s="127"/>
@@ -65591,10 +68418,10 @@
       <c r="K108" s="231">
         <v>2</v>
       </c>
-      <c r="L108" s="558" t="s">
+      <c r="L108" s="563" t="s">
         <v>86</v>
       </c>
-      <c r="M108" s="559"/>
+      <c r="M108" s="564"/>
       <c r="N108" s="232"/>
       <c r="O108" s="232"/>
       <c r="P108" s="232"/>
@@ -65704,15 +68531,15 @@
       </c>
       <c r="K112" s="233"/>
       <c r="L112" s="267"/>
-      <c r="M112" s="560" t="s">
+      <c r="M112" s="565" t="s">
         <v>85</v>
       </c>
-      <c r="N112" s="561"/>
-      <c r="O112" s="561"/>
-      <c r="P112" s="561"/>
-      <c r="Q112" s="561"/>
-      <c r="R112" s="561"/>
-      <c r="S112" s="562"/>
+      <c r="N112" s="566"/>
+      <c r="O112" s="566"/>
+      <c r="P112" s="566"/>
+      <c r="Q112" s="566"/>
+      <c r="R112" s="566"/>
+      <c r="S112" s="567"/>
       <c r="T112" s="232"/>
       <c r="U112" s="240"/>
       <c r="V112" s="240"/>
@@ -65729,13 +68556,13 @@
       <c r="J113" s="138"/>
       <c r="K113" s="233"/>
       <c r="L113" s="267"/>
-      <c r="M113" s="563"/>
-      <c r="N113" s="564"/>
-      <c r="O113" s="564"/>
-      <c r="P113" s="564"/>
-      <c r="Q113" s="564"/>
-      <c r="R113" s="564"/>
-      <c r="S113" s="565"/>
+      <c r="M113" s="568"/>
+      <c r="N113" s="569"/>
+      <c r="O113" s="569"/>
+      <c r="P113" s="569"/>
+      <c r="Q113" s="569"/>
+      <c r="R113" s="569"/>
+      <c r="S113" s="570"/>
       <c r="T113" s="232"/>
       <c r="U113" s="240"/>
       <c r="V113" s="240"/>
@@ -65760,13 +68587,13 @@
       <c r="J114" s="137"/>
       <c r="K114" s="233"/>
       <c r="L114" s="267"/>
-      <c r="M114" s="563"/>
-      <c r="N114" s="564"/>
-      <c r="O114" s="564"/>
-      <c r="P114" s="564"/>
-      <c r="Q114" s="564"/>
-      <c r="R114" s="564"/>
-      <c r="S114" s="565"/>
+      <c r="M114" s="568"/>
+      <c r="N114" s="569"/>
+      <c r="O114" s="569"/>
+      <c r="P114" s="569"/>
+      <c r="Q114" s="569"/>
+      <c r="R114" s="569"/>
+      <c r="S114" s="570"/>
       <c r="T114" s="232"/>
       <c r="U114" s="240"/>
       <c r="V114" s="240"/>
@@ -65783,13 +68610,13 @@
       <c r="J115" s="138"/>
       <c r="K115" s="233"/>
       <c r="L115" s="267"/>
-      <c r="M115" s="563"/>
-      <c r="N115" s="564"/>
-      <c r="O115" s="564"/>
-      <c r="P115" s="564"/>
-      <c r="Q115" s="564"/>
-      <c r="R115" s="564"/>
-      <c r="S115" s="565"/>
+      <c r="M115" s="568"/>
+      <c r="N115" s="569"/>
+      <c r="O115" s="569"/>
+      <c r="P115" s="569"/>
+      <c r="Q115" s="569"/>
+      <c r="R115" s="569"/>
+      <c r="S115" s="570"/>
       <c r="T115" s="232"/>
       <c r="U115" s="240"/>
       <c r="V115" s="240"/>
@@ -65808,13 +68635,13 @@
       <c r="J116" s="138"/>
       <c r="K116" s="233"/>
       <c r="L116" s="267"/>
-      <c r="M116" s="566"/>
-      <c r="N116" s="567"/>
-      <c r="O116" s="567"/>
-      <c r="P116" s="567"/>
-      <c r="Q116" s="567"/>
-      <c r="R116" s="567"/>
-      <c r="S116" s="568"/>
+      <c r="M116" s="571"/>
+      <c r="N116" s="572"/>
+      <c r="O116" s="572"/>
+      <c r="P116" s="572"/>
+      <c r="Q116" s="572"/>
+      <c r="R116" s="572"/>
+      <c r="S116" s="573"/>
       <c r="T116" s="232"/>
       <c r="U116" s="240"/>
       <c r="V116" s="240"/>
@@ -66200,10 +69027,10 @@
       <c r="B132" s="231">
         <v>3</v>
       </c>
-      <c r="C132" s="558" t="s">
+      <c r="C132" s="563" t="s">
         <v>87</v>
       </c>
-      <c r="D132" s="559"/>
+      <c r="D132" s="564"/>
       <c r="E132" s="232"/>
       <c r="F132" s="232"/>
       <c r="G132" s="232"/>
@@ -66212,10 +69039,10 @@
       <c r="J132" s="233"/>
       <c r="K132" s="233"/>
       <c r="L132" s="232"/>
-      <c r="M132" s="569" t="s">
+      <c r="M132" s="554" t="s">
         <v>109</v>
       </c>
-      <c r="N132" s="570"/>
+      <c r="N132" s="555"/>
       <c r="O132" s="234"/>
       <c r="P132" s="235"/>
       <c r="Q132" s="236"/>
@@ -66337,24 +69164,24 @@
     </row>
     <row r="137" spans="2:22" hidden="1">
       <c r="B137" s="241"/>
-      <c r="C137" s="552" t="s">
+      <c r="C137" s="557" t="s">
         <v>105</v>
       </c>
-      <c r="D137" s="553"/>
-      <c r="E137" s="554" t="s">
+      <c r="D137" s="558"/>
+      <c r="E137" s="559" t="s">
         <v>106</v>
       </c>
-      <c r="F137" s="554"/>
-      <c r="G137" s="553" t="s">
+      <c r="F137" s="559"/>
+      <c r="G137" s="558" t="s">
         <v>107</v>
       </c>
-      <c r="H137" s="553"/>
+      <c r="H137" s="558"/>
       <c r="I137" s="230"/>
       <c r="J137" s="233"/>
-      <c r="K137" s="555" t="s">
+      <c r="K137" s="560" t="s">
         <v>107</v>
       </c>
-      <c r="L137" s="555"/>
+      <c r="L137" s="560"/>
       <c r="M137" s="236"/>
       <c r="N137" s="235"/>
       <c r="O137" s="234"/>
@@ -66391,10 +69218,10 @@
     </row>
     <row r="139" spans="2:22" ht="15" hidden="1" thickBot="1">
       <c r="B139" s="245"/>
-      <c r="C139" s="569" t="s">
+      <c r="C139" s="554" t="s">
         <v>7</v>
       </c>
-      <c r="D139" s="570"/>
+      <c r="D139" s="555"/>
       <c r="E139" s="246" t="s">
         <v>67</v>
       </c>
@@ -66409,10 +69236,10 @@
       </c>
       <c r="I139" s="248"/>
       <c r="J139" s="249"/>
-      <c r="K139" s="572" t="s">
+      <c r="K139" s="556" t="s">
         <v>7</v>
       </c>
-      <c r="L139" s="572"/>
+      <c r="L139" s="556"/>
       <c r="M139" s="246" t="s">
         <v>67</v>
       </c>
@@ -66430,10 +69257,10 @@
     </row>
     <row r="140" spans="2:22" ht="15" hidden="1" thickBot="1">
       <c r="B140" s="241"/>
-      <c r="C140" s="571" t="s">
+      <c r="C140" s="553" t="s">
         <v>100</v>
       </c>
-      <c r="D140" s="571"/>
+      <c r="D140" s="553"/>
       <c r="E140" s="254" t="s">
         <v>76</v>
       </c>
@@ -66444,10 +69271,10 @@
       <c r="H140" s="256"/>
       <c r="I140" s="244"/>
       <c r="J140" s="233"/>
-      <c r="K140" s="571" t="s">
+      <c r="K140" s="553" t="s">
         <v>100</v>
       </c>
-      <c r="L140" s="571"/>
+      <c r="L140" s="553"/>
       <c r="M140" s="254" t="s">
         <v>76</v>
       </c>
@@ -66463,10 +69290,10 @@
     </row>
     <row r="141" spans="2:22" ht="15" hidden="1" thickBot="1">
       <c r="B141" s="241"/>
-      <c r="C141" s="571" t="s">
+      <c r="C141" s="553" t="s">
         <v>101</v>
       </c>
-      <c r="D141" s="571"/>
+      <c r="D141" s="553"/>
       <c r="E141" s="254" t="s">
         <v>77</v>
       </c>
@@ -66477,10 +69304,10 @@
       <c r="H141" s="256"/>
       <c r="I141" s="244"/>
       <c r="J141" s="233"/>
-      <c r="K141" s="571" t="s">
+      <c r="K141" s="553" t="s">
         <v>101</v>
       </c>
-      <c r="L141" s="571"/>
+      <c r="L141" s="553"/>
       <c r="M141" s="254" t="s">
         <v>77</v>
       </c>
@@ -66496,10 +69323,10 @@
     </row>
     <row r="142" spans="2:22" ht="15" hidden="1" thickBot="1">
       <c r="B142" s="241"/>
-      <c r="C142" s="571" t="s">
+      <c r="C142" s="553" t="s">
         <v>102</v>
       </c>
-      <c r="D142" s="571"/>
+      <c r="D142" s="553"/>
       <c r="E142" s="254" t="s">
         <v>78</v>
       </c>
@@ -66510,10 +69337,10 @@
       <c r="H142" s="256"/>
       <c r="I142" s="244"/>
       <c r="J142" s="233"/>
-      <c r="K142" s="571" t="s">
+      <c r="K142" s="553" t="s">
         <v>102</v>
       </c>
-      <c r="L142" s="571"/>
+      <c r="L142" s="553"/>
       <c r="M142" s="254" t="s">
         <v>78</v>
       </c>
@@ -66529,10 +69356,10 @@
     </row>
     <row r="143" spans="2:22" ht="15" hidden="1" thickBot="1">
       <c r="B143" s="241"/>
-      <c r="C143" s="571" t="s">
+      <c r="C143" s="553" t="s">
         <v>103</v>
       </c>
-      <c r="D143" s="571"/>
+      <c r="D143" s="553"/>
       <c r="E143" s="254" t="s">
         <v>79</v>
       </c>
@@ -66543,10 +69370,10 @@
       <c r="H143" s="256"/>
       <c r="I143" s="244"/>
       <c r="J143" s="233"/>
-      <c r="K143" s="571" t="s">
+      <c r="K143" s="553" t="s">
         <v>103</v>
       </c>
-      <c r="L143" s="571"/>
+      <c r="L143" s="553"/>
       <c r="M143" s="254" t="s">
         <v>79</v>
       </c>
@@ -67108,6 +69935,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="M112:S116"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="M132:N132"/>
     <mergeCell ref="C142:D142"/>
     <mergeCell ref="K142:L142"/>
     <mergeCell ref="C143:D143"/>
@@ -67118,15 +69954,6 @@
     <mergeCell ref="K140:L140"/>
     <mergeCell ref="C141:D141"/>
     <mergeCell ref="K141:L141"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="G137:H137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="L108:M108"/>
-    <mergeCell ref="M112:S116"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="M132:N132"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -71591,62 +74418,62 @@
       <c r="M53"/>
     </row>
     <row r="54" spans="8:13" ht="14.4">
-      <c r="I54" s="573" t="s">
+      <c r="I54" s="574" t="s">
         <v>634</v>
       </c>
-      <c r="J54" s="573"/>
-      <c r="K54" s="573"/>
-      <c r="L54" s="573"/>
+      <c r="J54" s="574"/>
+      <c r="K54" s="574"/>
+      <c r="L54" s="574"/>
       <c r="M54"/>
     </row>
     <row r="55" spans="8:13" ht="15.6" customHeight="1">
       <c r="H55">
         <v>2</v>
       </c>
-      <c r="I55" s="573"/>
-      <c r="J55" s="573"/>
-      <c r="K55" s="573"/>
-      <c r="L55" s="573"/>
+      <c r="I55" s="574"/>
+      <c r="J55" s="574"/>
+      <c r="K55" s="574"/>
+      <c r="L55" s="574"/>
       <c r="M55"/>
     </row>
     <row r="56" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I56" s="573"/>
-      <c r="J56" s="573"/>
-      <c r="K56" s="573"/>
-      <c r="L56" s="573"/>
+      <c r="I56" s="574"/>
+      <c r="J56" s="574"/>
+      <c r="K56" s="574"/>
+      <c r="L56" s="574"/>
       <c r="M56"/>
     </row>
     <row r="57" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I57" s="573"/>
-      <c r="J57" s="573"/>
-      <c r="K57" s="573"/>
-      <c r="L57" s="573"/>
+      <c r="I57" s="574"/>
+      <c r="J57" s="574"/>
+      <c r="K57" s="574"/>
+      <c r="L57" s="574"/>
       <c r="M57"/>
     </row>
     <row r="58" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I58" s="573"/>
-      <c r="J58" s="573"/>
-      <c r="K58" s="573"/>
-      <c r="L58" s="573"/>
+      <c r="I58" s="574"/>
+      <c r="J58" s="574"/>
+      <c r="K58" s="574"/>
+      <c r="L58" s="574"/>
       <c r="M58"/>
     </row>
     <row r="59" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I59" s="573"/>
-      <c r="J59" s="573"/>
-      <c r="K59" s="573"/>
-      <c r="L59" s="573"/>
+      <c r="I59" s="574"/>
+      <c r="J59" s="574"/>
+      <c r="K59" s="574"/>
+      <c r="L59" s="574"/>
     </row>
     <row r="60" spans="8:13">
-      <c r="I60" s="573"/>
-      <c r="J60" s="573"/>
-      <c r="K60" s="573"/>
-      <c r="L60" s="573"/>
+      <c r="I60" s="574"/>
+      <c r="J60" s="574"/>
+      <c r="K60" s="574"/>
+      <c r="L60" s="574"/>
     </row>
     <row r="61" spans="8:13">
-      <c r="I61" s="573"/>
-      <c r="J61" s="573"/>
-      <c r="K61" s="573"/>
-      <c r="L61" s="573"/>
+      <c r="I61" s="574"/>
+      <c r="J61" s="574"/>
+      <c r="K61" s="574"/>
+      <c r="L61" s="574"/>
     </row>
     <row r="63" spans="8:13">
       <c r="I63" s="294" t="s">
@@ -73762,62 +76589,62 @@
       <c r="M53"/>
     </row>
     <row r="54" spans="8:13" ht="14.4">
-      <c r="I54" s="573" t="s">
+      <c r="I54" s="574" t="s">
         <v>634</v>
       </c>
-      <c r="J54" s="573"/>
-      <c r="K54" s="573"/>
-      <c r="L54" s="573"/>
+      <c r="J54" s="574"/>
+      <c r="K54" s="574"/>
+      <c r="L54" s="574"/>
       <c r="M54"/>
     </row>
     <row r="55" spans="8:13" ht="15.6" customHeight="1">
       <c r="H55">
         <v>2</v>
       </c>
-      <c r="I55" s="573"/>
-      <c r="J55" s="573"/>
-      <c r="K55" s="573"/>
-      <c r="L55" s="573"/>
+      <c r="I55" s="574"/>
+      <c r="J55" s="574"/>
+      <c r="K55" s="574"/>
+      <c r="L55" s="574"/>
       <c r="M55"/>
     </row>
     <row r="56" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I56" s="573"/>
-      <c r="J56" s="573"/>
-      <c r="K56" s="573"/>
-      <c r="L56" s="573"/>
+      <c r="I56" s="574"/>
+      <c r="J56" s="574"/>
+      <c r="K56" s="574"/>
+      <c r="L56" s="574"/>
       <c r="M56"/>
     </row>
     <row r="57" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I57" s="573"/>
-      <c r="J57" s="573"/>
-      <c r="K57" s="573"/>
-      <c r="L57" s="573"/>
+      <c r="I57" s="574"/>
+      <c r="J57" s="574"/>
+      <c r="K57" s="574"/>
+      <c r="L57" s="574"/>
       <c r="M57"/>
     </row>
     <row r="58" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I58" s="573"/>
-      <c r="J58" s="573"/>
-      <c r="K58" s="573"/>
-      <c r="L58" s="573"/>
+      <c r="I58" s="574"/>
+      <c r="J58" s="574"/>
+      <c r="K58" s="574"/>
+      <c r="L58" s="574"/>
       <c r="M58"/>
     </row>
     <row r="59" spans="8:13" ht="15.6" customHeight="1">
-      <c r="I59" s="573"/>
-      <c r="J59" s="573"/>
-      <c r="K59" s="573"/>
-      <c r="L59" s="573"/>
+      <c r="I59" s="574"/>
+      <c r="J59" s="574"/>
+      <c r="K59" s="574"/>
+      <c r="L59" s="574"/>
     </row>
     <row r="60" spans="8:13">
-      <c r="I60" s="573"/>
-      <c r="J60" s="573"/>
-      <c r="K60" s="573"/>
-      <c r="L60" s="573"/>
+      <c r="I60" s="574"/>
+      <c r="J60" s="574"/>
+      <c r="K60" s="574"/>
+      <c r="L60" s="574"/>
     </row>
     <row r="61" spans="8:13">
-      <c r="I61" s="573"/>
-      <c r="J61" s="573"/>
-      <c r="K61" s="573"/>
-      <c r="L61" s="573"/>
+      <c r="I61" s="574"/>
+      <c r="J61" s="574"/>
+      <c r="K61" s="574"/>
+      <c r="L61" s="574"/>
     </row>
     <row r="63" spans="8:13">
       <c r="I63" s="294" t="s">
